--- a/dataset/Part 6_2_4_ Chronic Illness and Expenditure Tracking – Inpatient.xlsx
+++ b/dataset/Part 6_2_4_ Chronic Illness and Expenditure Tracking – Inpatient.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="68">
   <si>
     <t>ID</t>
   </si>
@@ -149,9 +149,6 @@
     <t>4 , NIMONIYA</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t xml:space="preserve">8 </t>
   </si>
   <si>
@@ -165,6 +162,9 @@
   </si>
   <si>
     <t>v4</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>v5</t>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>96 , JALBINDU</t>
+  </si>
+  <si>
+    <t>96 , PARALYSIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 </t>
   </si>
 </sst>
 </file>
@@ -571,7 +577,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:AA139"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5.855713" bestFit="true" customWidth="true" style="0"/>
@@ -594,7 +600,7 @@
     <col min="18" max="18" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="19" max="19" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="20" max="20" width="9.283447" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="6.998291" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="22" max="22" width="6.998291" bestFit="true" customWidth="true" style="0"/>
     <col min="23" max="23" width="6.998291" bestFit="true" customWidth="true" style="0"/>
     <col min="24" max="24" width="9.283447" bestFit="true" customWidth="true" style="0"/>
@@ -2662,13 +2668,13 @@
         <v>2881</v>
       </c>
       <c r="B29">
-        <v>2310</v>
+        <v>2110</v>
       </c>
       <c r="C29">
-        <v>20612</v>
+        <v>20807</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E29">
         <v>11</v>
@@ -2677,7 +2683,7 @@
         <v>41</v>
       </c>
       <c r="G29" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H29">
         <v>27</v>
@@ -2689,7 +2695,7 @@
         <v>2</v>
       </c>
       <c r="L29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -2754,7 +2760,7 @@
         <v>41</v>
       </c>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H30">
         <v>43</v>
@@ -2766,7 +2772,7 @@
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N30">
         <v>4200</v>
@@ -2813,7 +2819,7 @@
         <v>41</v>
       </c>
       <c r="G31" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H31">
         <v>43</v>
@@ -2825,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -2890,7 +2896,7 @@
         <v>41</v>
       </c>
       <c r="G32" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H32">
         <v>22</v>
@@ -2967,7 +2973,7 @@
         <v>41</v>
       </c>
       <c r="G33" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H33">
         <v>42</v>
@@ -2979,7 +2985,7 @@
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -3044,7 +3050,7 @@
         <v>41</v>
       </c>
       <c r="G34" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H34">
         <v>51</v>
@@ -3115,10 +3121,10 @@
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G35" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H35">
         <v>23</v>
@@ -3192,10 +3198,10 @@
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G36" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H36">
         <v>51</v>
@@ -3266,10 +3272,10 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G37" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H37">
         <v>56</v>
@@ -3340,10 +3346,10 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G38" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H38">
         <v>56</v>
@@ -3417,7 +3423,7 @@
         <v>50</v>
       </c>
       <c r="G39" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H39">
         <v>92</v>
@@ -3494,7 +3500,7 @@
         <v>50</v>
       </c>
       <c r="G40" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H40">
         <v>22</v>
@@ -3571,7 +3577,7 @@
         <v>50</v>
       </c>
       <c r="G41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H41">
         <v>28</v>
@@ -3624,7 +3630,7 @@
         <v>50</v>
       </c>
       <c r="G42" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H42">
         <v>28</v>
@@ -3698,7 +3704,7 @@
         <v>50</v>
       </c>
       <c r="G43" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H43">
         <v>28</v>
@@ -3742,7 +3748,7 @@
         <v>50</v>
       </c>
       <c r="G44" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H44">
         <v>53</v>
@@ -3807,7 +3813,7 @@
         <v>50</v>
       </c>
       <c r="G45" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H45">
         <v>53</v>
@@ -3872,7 +3878,7 @@
         <v>50</v>
       </c>
       <c r="G46" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H46">
         <v>53</v>
@@ -3937,7 +3943,7 @@
         <v>50</v>
       </c>
       <c r="G47" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H47">
         <v>53</v>
@@ -4002,7 +4008,7 @@
         <v>50</v>
       </c>
       <c r="G48" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H48">
         <v>53</v>
@@ -4067,7 +4073,7 @@
         <v>50</v>
       </c>
       <c r="G49" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H49">
         <v>53</v>
@@ -4132,7 +4138,7 @@
         <v>50</v>
       </c>
       <c r="G50" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H50">
         <v>53</v>
@@ -4197,7 +4203,7 @@
         <v>50</v>
       </c>
       <c r="G51" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H51">
         <v>53</v>
@@ -4262,7 +4268,7 @@
         <v>50</v>
       </c>
       <c r="G52" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H52">
         <v>53</v>
@@ -4327,7 +4333,7 @@
         <v>50</v>
       </c>
       <c r="G53" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H53">
         <v>53</v>
@@ -4466,7 +4472,7 @@
         <v>50</v>
       </c>
       <c r="G55" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H55">
         <v>12</v>
@@ -4513,7 +4519,7 @@
         <v>50</v>
       </c>
       <c r="G56" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H56">
         <v>24</v>
@@ -4587,7 +4593,7 @@
         <v>50</v>
       </c>
       <c r="G57" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H57">
         <v>26</v>
@@ -4652,7 +4658,7 @@
         <v>50</v>
       </c>
       <c r="G58" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H58">
         <v>52</v>
@@ -4729,7 +4735,7 @@
         <v>50</v>
       </c>
       <c r="G59" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H59">
         <v>91</v>
@@ -4741,7 +4747,7 @@
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N59">
         <v>0</v>
@@ -4806,7 +4812,7 @@
         <v>50</v>
       </c>
       <c r="G60" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H60">
         <v>92</v>
@@ -4883,7 +4889,7 @@
         <v>50</v>
       </c>
       <c r="G61" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H61">
         <v>92</v>
@@ -4895,7 +4901,7 @@
         <v>3</v>
       </c>
       <c r="L61" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N61">
         <v>25000</v>
@@ -4957,7 +4963,7 @@
         <v>50</v>
       </c>
       <c r="G62" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H62">
         <v>51</v>
@@ -5034,7 +5040,7 @@
         <v>50</v>
       </c>
       <c r="G63" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H63">
         <v>51</v>
@@ -5102,7 +5108,7 @@
         <v>50</v>
       </c>
       <c r="G64" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H64">
         <v>53</v>
@@ -5179,7 +5185,7 @@
         <v>50</v>
       </c>
       <c r="G65" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H65">
         <v>92</v>
@@ -5256,7 +5262,7 @@
         <v>50</v>
       </c>
       <c r="G66" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H66">
         <v>44</v>
@@ -5297,7 +5303,7 @@
         <v>50</v>
       </c>
       <c r="G67" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H67">
         <v>44</v>
@@ -5329,7 +5335,7 @@
         <v>50</v>
       </c>
       <c r="G68" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H68">
         <v>57</v>
@@ -5403,7 +5409,7 @@
         <v>50</v>
       </c>
       <c r="G69" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H69">
         <v>56</v>
@@ -5480,7 +5486,7 @@
         <v>50</v>
       </c>
       <c r="G70" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H70">
         <v>22</v>
@@ -5557,7 +5563,7 @@
         <v>50</v>
       </c>
       <c r="G71" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H71">
         <v>22</v>
@@ -5631,7 +5637,7 @@
         <v>50</v>
       </c>
       <c r="G72" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H72">
         <v>22</v>
@@ -5708,7 +5714,7 @@
         <v>50</v>
       </c>
       <c r="G73" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H73">
         <v>12</v>
@@ -5755,7 +5761,7 @@
         <v>50</v>
       </c>
       <c r="G74" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H74">
         <v>14</v>
@@ -5829,7 +5835,7 @@
         <v>50</v>
       </c>
       <c r="G75" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H75">
         <v>28</v>
@@ -5882,7 +5888,7 @@
         <v>50</v>
       </c>
       <c r="G76" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H76">
         <v>28</v>
@@ -5935,7 +5941,7 @@
         <v>50</v>
       </c>
       <c r="G77" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H77">
         <v>53</v>
@@ -6012,7 +6018,7 @@
         <v>50</v>
       </c>
       <c r="G78" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H78">
         <v>13</v>
@@ -6089,7 +6095,7 @@
         <v>50</v>
       </c>
       <c r="G79" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H79">
         <v>52</v>
@@ -6163,7 +6169,7 @@
         <v>50</v>
       </c>
       <c r="G80" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H80">
         <v>93</v>
@@ -6240,7 +6246,7 @@
         <v>50</v>
       </c>
       <c r="G81" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H81">
         <v>22</v>
@@ -6317,7 +6323,7 @@
         <v>50</v>
       </c>
       <c r="G82" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H82">
         <v>64</v>
@@ -6394,7 +6400,7 @@
         <v>50</v>
       </c>
       <c r="G83" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H83">
         <v>73</v>
@@ -6406,7 +6412,7 @@
         <v>6</v>
       </c>
       <c r="L83" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N83">
         <v>0</v>
@@ -6471,7 +6477,7 @@
         <v>50</v>
       </c>
       <c r="G84" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H84">
         <v>52</v>
@@ -6483,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="L84" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N84">
         <v>15000</v>
@@ -6548,7 +6554,7 @@
         <v>50</v>
       </c>
       <c r="G85" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H85">
         <v>52</v>
@@ -6625,7 +6631,7 @@
         <v>50</v>
       </c>
       <c r="G86" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H86">
         <v>12</v>
@@ -6669,7 +6675,7 @@
         <v>50</v>
       </c>
       <c r="G87" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H87">
         <v>42</v>
@@ -6746,7 +6752,7 @@
         <v>50</v>
       </c>
       <c r="G88" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H88">
         <v>42</v>
@@ -6784,7 +6790,7 @@
         <v>4675</v>
       </c>
       <c r="B89">
-        <v>3341</v>
+        <v>3390</v>
       </c>
       <c r="C89">
         <v>30704</v>
@@ -6799,7 +6805,7 @@
         <v>50</v>
       </c>
       <c r="G89" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H89">
         <v>51</v>
@@ -6873,7 +6879,7 @@
         <v>50</v>
       </c>
       <c r="G90" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H90">
         <v>51</v>
@@ -6950,7 +6956,7 @@
         <v>50</v>
       </c>
       <c r="G91" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H91">
         <v>42</v>
@@ -7024,7 +7030,7 @@
         <v>50</v>
       </c>
       <c r="G92" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H92">
         <v>51</v>
@@ -7056,7 +7062,7 @@
         <v>50</v>
       </c>
       <c r="G93" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H93">
         <v>24</v>
@@ -7130,7 +7136,7 @@
         <v>50</v>
       </c>
       <c r="G94" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H94">
         <v>24</v>
@@ -7204,7 +7210,7 @@
         <v>50</v>
       </c>
       <c r="G95" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H95">
         <v>13</v>
@@ -7254,7 +7260,7 @@
         <v>50</v>
       </c>
       <c r="G96" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H96">
         <v>14</v>
@@ -7331,7 +7337,7 @@
         <v>50</v>
       </c>
       <c r="G97" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H97">
         <v>51</v>
@@ -7405,7 +7411,7 @@
         <v>50</v>
       </c>
       <c r="G98" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H98">
         <v>51</v>
@@ -7476,7 +7482,7 @@
         <v>50</v>
       </c>
       <c r="G99" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H99">
         <v>56</v>
@@ -7523,7 +7529,7 @@
         <v>50</v>
       </c>
       <c r="G100" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H100">
         <v>53</v>
@@ -7600,7 +7606,7 @@
         <v>50</v>
       </c>
       <c r="G101" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H101">
         <v>53</v>
@@ -7677,7 +7683,7 @@
         <v>50</v>
       </c>
       <c r="G102" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H102">
         <v>53</v>
@@ -7754,7 +7760,7 @@
         <v>50</v>
       </c>
       <c r="G103" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H103">
         <v>28</v>
@@ -7798,7 +7804,7 @@
         <v>50</v>
       </c>
       <c r="G104" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H104">
         <v>28</v>
@@ -7842,7 +7848,7 @@
         <v>50</v>
       </c>
       <c r="G105" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H105">
         <v>41</v>
@@ -7919,7 +7925,7 @@
         <v>50</v>
       </c>
       <c r="G106" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H106">
         <v>53</v>
@@ -7996,7 +8002,7 @@
         <v>50</v>
       </c>
       <c r="G107" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H107">
         <v>43</v>
@@ -8025,114 +8031,126 @@
     </row>
     <row r="108" spans="1:27">
       <c r="A108">
-        <v>5024</v>
+        <v>5022</v>
       </c>
       <c r="B108">
-        <v>3103</v>
+        <v>4209</v>
       </c>
       <c r="C108">
-        <v>30212</v>
+        <v>41007</v>
       </c>
       <c r="D108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E108">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F108" t="s">
         <v>50</v>
       </c>
       <c r="G108" t="s">
+        <v>49</v>
+      </c>
+      <c r="H108">
         <v>44</v>
       </c>
-      <c r="H108">
-        <v>52</v>
-      </c>
       <c r="I108">
-        <v>22213</v>
+        <v>22198</v>
       </c>
       <c r="K108">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L108" t="s">
-        <v>45</v>
-      </c>
-      <c r="N108">
-        <v>2000</v>
-      </c>
-      <c r="O108">
-        <v>29000</v>
-      </c>
-      <c r="P108">
-        <v>0</v>
-      </c>
-      <c r="Q108">
-        <v>0</v>
-      </c>
-      <c r="R108">
-        <v>100000</v>
-      </c>
-      <c r="S108">
-        <v>0</v>
-      </c>
-      <c r="T108">
-        <v>10000</v>
-      </c>
-      <c r="U108">
-        <v>5000</v>
-      </c>
-      <c r="V108">
-        <v>5000</v>
-      </c>
-      <c r="W108">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="X108">
-        <v>151000</v>
+        <v>50000</v>
       </c>
       <c r="Y108" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Z108" t="s">
         <v>30</v>
       </c>
       <c r="AA108">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:27">
       <c r="A109">
-        <v>5058</v>
+        <v>5024</v>
       </c>
       <c r="B109">
-        <v>2208</v>
+        <v>3103</v>
       </c>
       <c r="C109">
-        <v>20614</v>
+        <v>30212</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F109" t="s">
         <v>50</v>
       </c>
       <c r="G109" t="s">
+        <v>49</v>
+      </c>
+      <c r="H109">
+        <v>52</v>
+      </c>
+      <c r="I109">
+        <v>22213</v>
+      </c>
+      <c r="K109">
+        <v>6</v>
+      </c>
+      <c r="L109" t="s">
         <v>44</v>
       </c>
-      <c r="H109">
-        <v>28</v>
-      </c>
-      <c r="I109">
-        <v>22395</v>
-      </c>
-      <c r="K109">
-        <v>1</v>
-      </c>
-      <c r="L109" t="s">
-        <v>35</v>
+      <c r="N109">
+        <v>2000</v>
+      </c>
+      <c r="O109">
+        <v>29000</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>0</v>
+      </c>
+      <c r="R109">
+        <v>100000</v>
+      </c>
+      <c r="S109">
+        <v>0</v>
+      </c>
+      <c r="T109">
+        <v>10000</v>
+      </c>
+      <c r="U109">
+        <v>5000</v>
+      </c>
+      <c r="V109">
+        <v>5000</v>
+      </c>
+      <c r="W109">
+        <v>0</v>
+      </c>
+      <c r="X109">
+        <v>151000</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA109">
+        <v>30</v>
       </c>
     </row>
     <row r="110" spans="1:27">
@@ -8155,7 +8173,7 @@
         <v>50</v>
       </c>
       <c r="G110" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H110">
         <v>28</v>
@@ -8190,16 +8208,16 @@
         <v>50</v>
       </c>
       <c r="G111" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H111">
         <v>28</v>
       </c>
       <c r="I111">
-        <v>22396</v>
+        <v>22395</v>
       </c>
       <c r="K111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L111" t="s">
         <v>35</v>
@@ -8225,7 +8243,7 @@
         <v>50</v>
       </c>
       <c r="G112" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H112">
         <v>28</v>
@@ -8260,16 +8278,16 @@
         <v>50</v>
       </c>
       <c r="G113" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H113">
         <v>28</v>
       </c>
       <c r="I113">
-        <v>22398</v>
+        <v>22396</v>
       </c>
       <c r="K113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L113" t="s">
         <v>35</v>
@@ -8277,46 +8295,37 @@
     </row>
     <row r="114" spans="1:27">
       <c r="A114">
-        <v>5104</v>
+        <v>5058</v>
       </c>
       <c r="B114">
-        <v>3103</v>
+        <v>2208</v>
       </c>
       <c r="C114">
-        <v>30212</v>
+        <v>20614</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F114" t="s">
         <v>50</v>
       </c>
       <c r="G114" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H114">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="I114">
-        <v>22635</v>
+        <v>22398</v>
       </c>
       <c r="K114">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L114" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y114" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z114" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA114">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="115" spans="1:27">
@@ -8339,362 +8348,326 @@
         <v>50</v>
       </c>
       <c r="G115" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H115">
         <v>52</v>
       </c>
       <c r="I115">
-        <v>22639</v>
+        <v>22635</v>
       </c>
       <c r="K115">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L115" t="s">
-        <v>29</v>
-      </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>0</v>
-      </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-      <c r="Q115">
-        <v>0</v>
-      </c>
-      <c r="R115">
-        <v>3000</v>
-      </c>
-      <c r="S115">
-        <v>0</v>
-      </c>
-      <c r="U115">
-        <v>2500</v>
-      </c>
-      <c r="V115">
-        <v>0</v>
-      </c>
-      <c r="W115">
-        <v>0</v>
-      </c>
-      <c r="X115">
-        <v>5500</v>
+        <v>44</v>
       </c>
       <c r="Y115" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="Z115" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="AA115">
+        <v>45</v>
       </c>
     </row>
     <row r="116" spans="1:27">
       <c r="A116">
-        <v>5115</v>
+        <v>5104</v>
       </c>
       <c r="B116">
-        <v>2110</v>
+        <v>3103</v>
       </c>
       <c r="C116">
-        <v>20807</v>
+        <v>30212</v>
       </c>
       <c r="D116">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E116">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F116" t="s">
         <v>50</v>
       </c>
       <c r="G116" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H116">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="I116">
-        <v>22705</v>
+        <v>22639</v>
       </c>
       <c r="K116">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L116" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N116">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="O116">
         <v>0</v>
       </c>
       <c r="P116">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="Q116">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="R116">
-        <v>50000</v>
-      </c>
-      <c r="T116">
-        <v>15000</v>
+        <v>3000</v>
+      </c>
+      <c r="S116">
+        <v>0</v>
       </c>
       <c r="U116">
-        <v>8000</v>
+        <v>2500</v>
       </c>
       <c r="V116">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="W116">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X116">
-        <v>100000</v>
+        <v>5500</v>
       </c>
       <c r="Y116" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z116" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA116">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:27">
       <c r="A117">
-        <v>5116</v>
+        <v>5108</v>
       </c>
       <c r="B117">
-        <v>2110</v>
+        <v>4203</v>
       </c>
       <c r="C117">
-        <v>20807</v>
+        <v>40602</v>
       </c>
       <c r="D117">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E117">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F117" t="s">
         <v>50</v>
       </c>
       <c r="G117" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H117">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I117">
-        <v>22712</v>
+        <v>22655</v>
       </c>
       <c r="K117">
         <v>1</v>
       </c>
       <c r="L117" t="s">
-        <v>29</v>
-      </c>
-      <c r="N117">
-        <v>0</v>
-      </c>
-      <c r="O117">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="Q117">
-        <v>80</v>
+        <v>100000</v>
       </c>
       <c r="R117">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="S117">
-        <v>510</v>
+        <v>85000</v>
       </c>
       <c r="T117">
-        <v>1400</v>
+        <v>72000</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>104500</v>
       </c>
       <c r="V117">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W117">
         <v>0</v>
       </c>
       <c r="X117">
-        <v>18000</v>
+        <v>600000</v>
       </c>
       <c r="Y117" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z117" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="AA117">
+        <v>90</v>
       </c>
     </row>
     <row r="118" spans="1:27">
       <c r="A118">
-        <v>5127</v>
+        <v>5115</v>
       </c>
       <c r="B118">
-        <v>3103</v>
+        <v>2110</v>
       </c>
       <c r="C118">
-        <v>30212</v>
+        <v>20807</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E118">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F118" t="s">
         <v>50</v>
       </c>
       <c r="G118" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H118">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="I118">
-        <v>22792</v>
+        <v>22705</v>
       </c>
       <c r="K118">
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N118">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="O118">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="R118">
+        <v>50000</v>
+      </c>
+      <c r="T118">
+        <v>15000</v>
+      </c>
+      <c r="U118">
+        <v>8000</v>
+      </c>
+      <c r="V118">
         <v>5000</v>
       </c>
-      <c r="S118">
-        <v>0</v>
-      </c>
-      <c r="T118">
+      <c r="W118">
         <v>5000</v>
       </c>
-      <c r="U118">
-        <v>200</v>
-      </c>
-      <c r="V118">
-        <v>0</v>
-      </c>
-      <c r="W118">
-        <v>0</v>
-      </c>
       <c r="X118">
-        <v>11700</v>
+        <v>100000</v>
       </c>
       <c r="Y118" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z118" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="AA118">
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:27">
       <c r="A119">
-        <v>5162</v>
+        <v>5116</v>
       </c>
       <c r="B119">
-        <v>3103</v>
+        <v>2110</v>
       </c>
       <c r="C119">
-        <v>30212</v>
+        <v>20807</v>
       </c>
       <c r="D119">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E119">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F119" t="s">
         <v>50</v>
       </c>
       <c r="G119" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H119">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I119">
-        <v>22974</v>
+        <v>22712</v>
       </c>
       <c r="K119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L119" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="N119">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P119">
         <v>0</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="T119">
-        <v>2000</v>
+        <v>1400</v>
       </c>
       <c r="U119">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="V119">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="W119">
         <v>0</v>
       </c>
       <c r="X119">
-        <v>38500</v>
+        <v>18000</v>
       </c>
       <c r="Y119" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z119" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA119">
-        <v>80</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="1:27">
       <c r="A120">
-        <v>5169</v>
+        <v>5127</v>
       </c>
       <c r="B120">
-        <v>3203</v>
+        <v>3103</v>
       </c>
       <c r="C120">
         <v>30212</v>
@@ -8703,31 +8676,31 @@
         <v>1</v>
       </c>
       <c r="E120">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F120" t="s">
         <v>50</v>
       </c>
       <c r="G120" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H120">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I120">
-        <v>23011</v>
+        <v>22792</v>
       </c>
       <c r="K120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L120" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="N120">
-        <v>95000</v>
+        <v>500</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -8736,213 +8709,240 @@
         <v>0</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="S120">
         <v>0</v>
       </c>
       <c r="T120">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="U120">
-        <v>5000</v>
+        <v>200</v>
       </c>
       <c r="V120">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="W120">
         <v>0</v>
       </c>
       <c r="X120">
-        <v>110000</v>
+        <v>11700</v>
       </c>
       <c r="Y120" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z120" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA120">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" spans="1:27">
       <c r="A121">
-        <v>5176</v>
+        <v>5162</v>
       </c>
       <c r="B121">
-        <v>2110</v>
+        <v>3103</v>
       </c>
       <c r="C121">
-        <v>20807</v>
+        <v>30212</v>
       </c>
       <c r="D121">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E121">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F121" t="s">
         <v>50</v>
       </c>
       <c r="G121" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H121">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="I121">
-        <v>23064</v>
+        <v>22974</v>
       </c>
       <c r="K121">
         <v>2</v>
       </c>
       <c r="L121" t="s">
-        <v>30</v>
+        <v>64</v>
+      </c>
+      <c r="N121">
+        <v>33000</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>0</v>
+      </c>
+      <c r="R121">
+        <v>0</v>
+      </c>
+      <c r="S121">
+        <v>0</v>
+      </c>
+      <c r="T121">
+        <v>2000</v>
+      </c>
+      <c r="U121">
+        <v>1500</v>
+      </c>
+      <c r="V121">
+        <v>2000</v>
+      </c>
+      <c r="W121">
+        <v>0</v>
       </c>
       <c r="X121">
-        <v>50000</v>
+        <v>38500</v>
       </c>
       <c r="Y121" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z121" t="s">
         <v>30</v>
       </c>
       <c r="AA121">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="122" spans="1:27">
       <c r="A122">
-        <v>5176</v>
+        <v>5169</v>
       </c>
       <c r="B122">
-        <v>2110</v>
+        <v>3203</v>
       </c>
       <c r="C122">
-        <v>20807</v>
+        <v>30212</v>
       </c>
       <c r="D122">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E122">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F122" t="s">
         <v>50</v>
       </c>
       <c r="G122" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H122">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="I122">
-        <v>23070</v>
+        <v>23011</v>
       </c>
       <c r="K122">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L122" t="s">
-        <v>30</v>
+        <v>59</v>
+      </c>
+      <c r="N122">
+        <v>95000</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>0</v>
+      </c>
+      <c r="R122">
+        <v>0</v>
+      </c>
+      <c r="S122">
+        <v>0</v>
+      </c>
+      <c r="T122">
+        <v>4000</v>
+      </c>
+      <c r="U122">
+        <v>5000</v>
+      </c>
+      <c r="V122">
+        <v>6000</v>
+      </c>
+      <c r="W122">
+        <v>0</v>
       </c>
       <c r="X122">
-        <v>20000</v>
+        <v>110000</v>
       </c>
       <c r="Y122" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z122" t="s">
         <v>30</v>
       </c>
       <c r="AA122">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123" spans="1:27">
       <c r="A123">
-        <v>5223</v>
+        <v>5176</v>
       </c>
       <c r="B123">
-        <v>7108</v>
+        <v>2110</v>
       </c>
       <c r="C123">
-        <v>70901</v>
+        <v>20807</v>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E123">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F123" t="s">
         <v>50</v>
       </c>
       <c r="G123" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H123">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="I123">
-        <v>23277</v>
+        <v>23064</v>
       </c>
       <c r="K123">
         <v>2</v>
       </c>
       <c r="L123" t="s">
-        <v>45</v>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <v>0</v>
-      </c>
-      <c r="R123">
-        <v>0</v>
-      </c>
-      <c r="S123">
-        <v>0</v>
-      </c>
-      <c r="T123">
-        <v>7000</v>
-      </c>
-      <c r="U123">
-        <v>10000</v>
-      </c>
-      <c r="V123">
-        <v>0</v>
-      </c>
-      <c r="W123">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="X123">
-        <v>77400</v>
+        <v>50000</v>
       </c>
       <c r="Y123" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z123" t="s">
         <v>30</v>
       </c>
       <c r="AA123">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:27">
       <c r="A124">
-        <v>5272</v>
+        <v>5176</v>
       </c>
       <c r="B124">
-        <v>2210</v>
+        <v>2110</v>
       </c>
       <c r="C124">
         <v>20807</v>
@@ -8951,34 +8951,28 @@
         <v>26</v>
       </c>
       <c r="E124">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F124" t="s">
         <v>50</v>
       </c>
       <c r="G124" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H124">
         <v>28</v>
       </c>
       <c r="I124">
-        <v>23543</v>
+        <v>23070</v>
       </c>
       <c r="K124">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L124" t="s">
-        <v>62</v>
-      </c>
-      <c r="N124">
-        <v>90000</v>
-      </c>
-      <c r="W124">
-        <v>10000</v>
+        <v>30</v>
       </c>
       <c r="X124">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="Y124" t="s">
         <v>30</v>
@@ -8987,229 +8981,961 @@
         <v>30</v>
       </c>
       <c r="AA124">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:27">
       <c r="A125">
-        <v>5530</v>
+        <v>5223</v>
       </c>
       <c r="B125">
-        <v>3203</v>
+        <v>7108</v>
       </c>
       <c r="C125">
-        <v>30212</v>
+        <v>70901</v>
       </c>
       <c r="D125">
         <v>3</v>
       </c>
       <c r="E125">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F125" t="s">
         <v>50</v>
       </c>
       <c r="G125" t="s">
+        <v>49</v>
+      </c>
+      <c r="H125">
+        <v>74</v>
+      </c>
+      <c r="I125">
+        <v>23277</v>
+      </c>
+      <c r="K125">
+        <v>2</v>
+      </c>
+      <c r="L125" t="s">
         <v>44</v>
       </c>
-      <c r="H125">
-        <v>52</v>
-      </c>
-      <c r="I125">
-        <v>24937</v>
-      </c>
-      <c r="K125">
-        <v>1</v>
-      </c>
-      <c r="L125" t="s">
-        <v>65</v>
-      </c>
       <c r="N125">
         <v>0</v>
       </c>
       <c r="O125">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P125">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q125">
         <v>0</v>
       </c>
       <c r="R125">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="S125">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="T125">
-        <v>1600</v>
+        <v>7000</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V125">
         <v>0</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X125">
-        <v>4200</v>
+        <v>77400</v>
       </c>
       <c r="Y125" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z125" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="AA125">
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:27">
       <c r="A126">
-        <v>5530</v>
+        <v>5258</v>
       </c>
       <c r="B126">
-        <v>3203</v>
+        <v>4101</v>
       </c>
       <c r="C126">
-        <v>30212</v>
+        <v>40204</v>
       </c>
       <c r="D126">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E126">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F126" t="s">
         <v>50</v>
       </c>
       <c r="G126" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H126">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I126">
-        <v>24937</v>
+        <v>23462</v>
       </c>
       <c r="K126">
         <v>1</v>
       </c>
       <c r="L126" t="s">
-        <v>32</v>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>100</v>
-      </c>
-      <c r="P126">
-        <v>100</v>
-      </c>
-      <c r="Q126">
-        <v>0</v>
-      </c>
-      <c r="R126">
-        <v>500</v>
-      </c>
-      <c r="S126">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="T126">
-        <v>800</v>
+        <v>5400</v>
       </c>
       <c r="U126">
-        <v>0</v>
-      </c>
-      <c r="V126">
-        <v>0</v>
-      </c>
-      <c r="W126">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X126">
-        <v>1500</v>
+        <v>70000</v>
       </c>
       <c r="Y126" t="s">
         <v>30</v>
       </c>
       <c r="Z126" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="AA126">
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:27">
       <c r="A127">
+        <v>5272</v>
+      </c>
+      <c r="B127">
+        <v>2210</v>
+      </c>
+      <c r="C127">
+        <v>20807</v>
+      </c>
+      <c r="D127">
+        <v>26</v>
+      </c>
+      <c r="E127">
+        <v>19</v>
+      </c>
+      <c r="F127" t="s">
+        <v>50</v>
+      </c>
+      <c r="G127" t="s">
+        <v>49</v>
+      </c>
+      <c r="H127">
+        <v>28</v>
+      </c>
+      <c r="I127">
+        <v>23543</v>
+      </c>
+      <c r="K127">
+        <v>4</v>
+      </c>
+      <c r="L127" t="s">
+        <v>62</v>
+      </c>
+      <c r="N127">
+        <v>90000</v>
+      </c>
+      <c r="W127">
+        <v>10000</v>
+      </c>
+      <c r="X127">
+        <v>100000</v>
+      </c>
+      <c r="Y127" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA127">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:27">
+      <c r="A128">
         <v>5530</v>
       </c>
-      <c r="B127">
+      <c r="B128">
         <v>3203</v>
       </c>
-      <c r="C127">
+      <c r="C128">
         <v>30212</v>
       </c>
-      <c r="D127">
+      <c r="D128">
         <v>3</v>
       </c>
-      <c r="E127">
+      <c r="E128">
         <v>13</v>
       </c>
-      <c r="F127" t="s">
-        <v>50</v>
-      </c>
-      <c r="G127" t="s">
-        <v>44</v>
-      </c>
-      <c r="H127">
+      <c r="F128" t="s">
+        <v>50</v>
+      </c>
+      <c r="G128" t="s">
+        <v>49</v>
+      </c>
+      <c r="H128">
         <v>52</v>
       </c>
-      <c r="I127">
+      <c r="I128">
         <v>24937</v>
       </c>
-      <c r="K127">
+      <c r="K128">
         <v>1</v>
       </c>
-      <c r="L127" t="s">
+      <c r="L128" t="s">
+        <v>65</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>400</v>
+      </c>
+      <c r="P128">
+        <v>100</v>
+      </c>
+      <c r="Q128">
+        <v>0</v>
+      </c>
+      <c r="R128">
+        <v>500</v>
+      </c>
+      <c r="S128">
+        <v>1600</v>
+      </c>
+      <c r="T128">
+        <v>1600</v>
+      </c>
+      <c r="U128">
+        <v>0</v>
+      </c>
+      <c r="V128">
+        <v>0</v>
+      </c>
+      <c r="W128">
+        <v>0</v>
+      </c>
+      <c r="X128">
+        <v>4200</v>
+      </c>
+      <c r="Y128" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="129" spans="1:27">
+      <c r="A129">
+        <v>5530</v>
+      </c>
+      <c r="B129">
+        <v>3203</v>
+      </c>
+      <c r="C129">
+        <v>30212</v>
+      </c>
+      <c r="D129">
+        <v>3</v>
+      </c>
+      <c r="E129">
+        <v>13</v>
+      </c>
+      <c r="F129" t="s">
+        <v>50</v>
+      </c>
+      <c r="G129" t="s">
+        <v>49</v>
+      </c>
+      <c r="H129">
+        <v>52</v>
+      </c>
+      <c r="I129">
+        <v>24937</v>
+      </c>
+      <c r="K129">
+        <v>1</v>
+      </c>
+      <c r="L129" t="s">
+        <v>32</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>100</v>
+      </c>
+      <c r="P129">
+        <v>100</v>
+      </c>
+      <c r="Q129">
+        <v>0</v>
+      </c>
+      <c r="R129">
+        <v>500</v>
+      </c>
+      <c r="S129">
+        <v>0</v>
+      </c>
+      <c r="T129">
+        <v>800</v>
+      </c>
+      <c r="U129">
+        <v>0</v>
+      </c>
+      <c r="V129">
+        <v>0</v>
+      </c>
+      <c r="W129">
+        <v>0</v>
+      </c>
+      <c r="X129">
+        <v>1500</v>
+      </c>
+      <c r="Y129" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="130" spans="1:27">
+      <c r="A130">
+        <v>5530</v>
+      </c>
+      <c r="B130">
+        <v>3203</v>
+      </c>
+      <c r="C130">
+        <v>30212</v>
+      </c>
+      <c r="D130">
+        <v>3</v>
+      </c>
+      <c r="E130">
+        <v>13</v>
+      </c>
+      <c r="F130" t="s">
+        <v>50</v>
+      </c>
+      <c r="G130" t="s">
+        <v>49</v>
+      </c>
+      <c r="H130">
+        <v>52</v>
+      </c>
+      <c r="I130">
+        <v>24937</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130" t="s">
         <v>33</v>
       </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>0</v>
-      </c>
-      <c r="R127">
-        <v>0</v>
-      </c>
-      <c r="S127">
-        <v>0</v>
-      </c>
-      <c r="T127">
-        <v>0</v>
-      </c>
-      <c r="U127">
-        <v>0</v>
-      </c>
-      <c r="V127">
-        <v>0</v>
-      </c>
-      <c r="W127">
-        <v>0</v>
-      </c>
-      <c r="X127">
-        <v>0</v>
-      </c>
-      <c r="Y127" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z127" t="s">
-        <v>32</v>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>0</v>
+      </c>
+      <c r="R130">
+        <v>0</v>
+      </c>
+      <c r="S130">
+        <v>0</v>
+      </c>
+      <c r="T130">
+        <v>0</v>
+      </c>
+      <c r="U130">
+        <v>0</v>
+      </c>
+      <c r="V130">
+        <v>0</v>
+      </c>
+      <c r="W130">
+        <v>0</v>
+      </c>
+      <c r="X130">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="131" spans="1:27">
+      <c r="A131">
+        <v>5750</v>
+      </c>
+      <c r="B131">
+        <v>3108</v>
+      </c>
+      <c r="C131">
+        <v>30802</v>
+      </c>
+      <c r="D131">
+        <v>27</v>
+      </c>
+      <c r="E131">
+        <v>26</v>
+      </c>
+      <c r="F131" t="s">
+        <v>50</v>
+      </c>
+      <c r="G131" t="s">
+        <v>49</v>
+      </c>
+      <c r="H131">
+        <v>56</v>
+      </c>
+      <c r="I131">
+        <v>26059</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="L131" t="s">
+        <v>32</v>
+      </c>
+      <c r="X131">
+        <v>40000</v>
+      </c>
+      <c r="Y131" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z131" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA131">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:27">
+      <c r="A132">
+        <v>5768</v>
+      </c>
+      <c r="B132">
+        <v>4209</v>
+      </c>
+      <c r="C132">
+        <v>41007</v>
+      </c>
+      <c r="D132">
+        <v>4</v>
+      </c>
+      <c r="E132">
+        <v>21</v>
+      </c>
+      <c r="F132" t="s">
+        <v>50</v>
+      </c>
+      <c r="G132" t="s">
+        <v>49</v>
+      </c>
+      <c r="H132">
+        <v>42</v>
+      </c>
+      <c r="I132">
+        <v>26151</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132" t="s">
+        <v>34</v>
+      </c>
+      <c r="X132">
+        <v>200000</v>
+      </c>
+      <c r="Y132" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133" spans="1:27">
+      <c r="A133">
+        <v>5777</v>
+      </c>
+      <c r="B133">
+        <v>4109</v>
+      </c>
+      <c r="C133">
+        <v>41007</v>
+      </c>
+      <c r="D133">
+        <v>4</v>
+      </c>
+      <c r="E133">
+        <v>18</v>
+      </c>
+      <c r="F133" t="s">
+        <v>50</v>
+      </c>
+      <c r="G133" t="s">
+        <v>49</v>
+      </c>
+      <c r="H133">
+        <v>42</v>
+      </c>
+      <c r="I133">
+        <v>26202</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133" t="s">
+        <v>66</v>
+      </c>
+      <c r="O133">
+        <v>300000</v>
+      </c>
+      <c r="X133">
+        <v>300000</v>
+      </c>
+      <c r="Y133" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="134" spans="1:27">
+      <c r="A134">
+        <v>5814</v>
+      </c>
+      <c r="B134">
+        <v>5321</v>
+      </c>
+      <c r="C134">
+        <v>50802</v>
+      </c>
+      <c r="D134">
+        <v>10</v>
+      </c>
+      <c r="E134">
+        <v>11</v>
+      </c>
+      <c r="F134" t="s">
+        <v>50</v>
+      </c>
+      <c r="G134" t="s">
+        <v>49</v>
+      </c>
+      <c r="H134">
+        <v>54</v>
+      </c>
+      <c r="I134">
+        <v>26409</v>
+      </c>
+      <c r="K134">
+        <v>4</v>
+      </c>
+      <c r="L134" t="s">
+        <v>67</v>
+      </c>
+      <c r="N134">
+        <v>5000</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134">
+        <v>0</v>
+      </c>
+      <c r="S134">
+        <v>0</v>
+      </c>
+      <c r="T134">
+        <v>0</v>
+      </c>
+      <c r="U134">
+        <v>0</v>
+      </c>
+      <c r="V134">
+        <v>0</v>
+      </c>
+      <c r="W134">
+        <v>2000</v>
+      </c>
+      <c r="X134">
+        <v>7000</v>
+      </c>
+      <c r="Y134" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z134" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="135" spans="1:27">
+      <c r="A135">
+        <v>5834</v>
+      </c>
+      <c r="B135">
+        <v>4109</v>
+      </c>
+      <c r="C135">
+        <v>41007</v>
+      </c>
+      <c r="D135">
+        <v>4</v>
+      </c>
+      <c r="E135">
+        <v>13</v>
+      </c>
+      <c r="F135" t="s">
+        <v>50</v>
+      </c>
+      <c r="G135" t="s">
+        <v>49</v>
+      </c>
+      <c r="H135">
+        <v>41</v>
+      </c>
+      <c r="I135">
+        <v>26524</v>
+      </c>
+      <c r="K135">
+        <v>2</v>
+      </c>
+      <c r="L135" t="s">
+        <v>30</v>
+      </c>
+      <c r="N135">
+        <v>3000</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="X135">
+        <v>200000</v>
+      </c>
+      <c r="Y135" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z135" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA135">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:27">
+      <c r="A136">
+        <v>5892</v>
+      </c>
+      <c r="B136">
+        <v>2209</v>
+      </c>
+      <c r="C136">
+        <v>20703</v>
+      </c>
+      <c r="D136">
+        <v>10</v>
+      </c>
+      <c r="E136">
+        <v>22</v>
+      </c>
+      <c r="F136" t="s">
+        <v>50</v>
+      </c>
+      <c r="G136" t="s">
+        <v>49</v>
+      </c>
+      <c r="H136">
+        <v>26</v>
+      </c>
+      <c r="I136">
+        <v>26873</v>
+      </c>
+      <c r="K136">
+        <v>6</v>
+      </c>
+      <c r="L136" t="s">
+        <v>35</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>700</v>
+      </c>
+      <c r="Q136">
+        <v>10000</v>
+      </c>
+      <c r="R136">
+        <v>15000</v>
+      </c>
+      <c r="S136">
+        <v>2000</v>
+      </c>
+      <c r="T136">
+        <v>5000</v>
+      </c>
+      <c r="U136">
+        <v>3000</v>
+      </c>
+      <c r="V136">
+        <v>2000</v>
+      </c>
+      <c r="W136">
+        <v>2300</v>
+      </c>
+      <c r="X136">
+        <v>40000</v>
+      </c>
+      <c r="Y136" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="137" spans="1:27">
+      <c r="A137">
+        <v>5894</v>
+      </c>
+      <c r="B137">
+        <v>2209</v>
+      </c>
+      <c r="C137">
+        <v>20703</v>
+      </c>
+      <c r="D137">
+        <v>10</v>
+      </c>
+      <c r="E137">
+        <v>23</v>
+      </c>
+      <c r="F137" t="s">
+        <v>50</v>
+      </c>
+      <c r="G137" t="s">
+        <v>49</v>
+      </c>
+      <c r="H137">
+        <v>26</v>
+      </c>
+      <c r="I137">
+        <v>26885</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
+      <c r="L137" t="s">
+        <v>30</v>
+      </c>
+      <c r="P137">
+        <v>8000</v>
+      </c>
+      <c r="Q137">
+        <v>25000</v>
+      </c>
+      <c r="R137">
+        <v>30000</v>
+      </c>
+      <c r="S137">
+        <v>5000</v>
+      </c>
+      <c r="T137">
+        <v>8000</v>
+      </c>
+      <c r="U137">
+        <v>7000</v>
+      </c>
+      <c r="V137">
+        <v>5000</v>
+      </c>
+      <c r="W137">
+        <v>2000</v>
+      </c>
+      <c r="X137">
+        <v>90000</v>
+      </c>
+      <c r="Y137" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA137">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:27">
+      <c r="A138">
+        <v>5977</v>
+      </c>
+      <c r="B138">
+        <v>2209</v>
+      </c>
+      <c r="C138">
+        <v>20703</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+      <c r="E138">
+        <v>33</v>
+      </c>
+      <c r="F138" t="s">
+        <v>50</v>
+      </c>
+      <c r="G138" t="s">
+        <v>49</v>
+      </c>
+      <c r="H138">
+        <v>26</v>
+      </c>
+      <c r="I138">
+        <v>27380</v>
+      </c>
+      <c r="K138">
+        <v>5</v>
+      </c>
+      <c r="L138" t="s">
+        <v>33</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>300</v>
+      </c>
+      <c r="P138">
+        <v>5000</v>
+      </c>
+      <c r="Q138">
+        <v>4700</v>
+      </c>
+      <c r="R138">
+        <v>20000</v>
+      </c>
+      <c r="S138">
+        <v>5000</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="X138">
+        <v>35000</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="139" spans="1:27">
+      <c r="A139">
+        <v>6008</v>
+      </c>
+      <c r="B139">
+        <v>6104</v>
+      </c>
+      <c r="C139">
+        <v>60608</v>
+      </c>
+      <c r="D139">
+        <v>3</v>
+      </c>
+      <c r="E139">
+        <v>4</v>
+      </c>
+      <c r="F139" t="s">
+        <v>50</v>
+      </c>
+      <c r="G139" t="s">
+        <v>49</v>
+      </c>
+      <c r="H139">
+        <v>61</v>
+      </c>
+      <c r="I139">
+        <v>27547</v>
+      </c>
+      <c r="K139">
+        <v>4</v>
+      </c>
+      <c r="L139" t="s">
+        <v>39</v>
+      </c>
+      <c r="N139">
+        <v>20</v>
+      </c>
+      <c r="O139">
+        <v>60</v>
+      </c>
+      <c r="P139">
+        <v>2000</v>
+      </c>
+      <c r="Q139">
+        <v>1500</v>
+      </c>
+      <c r="R139">
+        <v>48000</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>22000</v>
+      </c>
+      <c r="U139">
+        <v>11420</v>
+      </c>
+      <c r="V139">
+        <v>6000</v>
+      </c>
+      <c r="W139">
+        <v>5000</v>
+      </c>
+      <c r="X139">
+        <v>96000</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA139">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/Part 6_2_4_ Chronic Illness and Expenditure Tracking – Inpatient.xlsx
+++ b/dataset/Part 6_2_4_ Chronic Illness and Expenditure Tracking – Inpatient.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-06\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-18-today\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5801E7F-B1DF-4A23-8BC8-792477165D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D8B644-8ACD-4C20-9372-41A73130A95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="261">
   <si>
     <t>ID</t>
   </si>
@@ -769,6 +769,51 @@
   </si>
   <si>
     <t>0b21cf90-0f66-4706-8aa5-d53a4f499f78</t>
+  </si>
+  <si>
+    <t>c4ff2eee-2672-457d-bc2d-00a9610a13d6</t>
+  </si>
+  <si>
+    <t>fd3841e8-fd1c-480a-af53-385c5bba413c</t>
+  </si>
+  <si>
+    <t>3cf1e664-02f4-43d8-9261-94eeefa3de25</t>
+  </si>
+  <si>
+    <t>96, PROSTATE</t>
+  </si>
+  <si>
+    <t>bd352ff8-7263-4d60-b580-22960a06dbe3</t>
+  </si>
+  <si>
+    <t>7365075f-4d33-4986-84e9-4761256a3653</t>
+  </si>
+  <si>
+    <t>37d59658-0f94-4b20-b7ec-024169155e94</t>
+  </si>
+  <si>
+    <t>bcae1372-2e7b-4964-934b-9d1166648390</t>
+  </si>
+  <si>
+    <t>3aa9d2cc-03ae-4ccc-9ccd-776b35db43a7</t>
+  </si>
+  <si>
+    <t>95e2df04-cd64-478d-a61c-dba0501ffea8</t>
+  </si>
+  <si>
+    <t>8cc8075b-d3a2-48f6-b5f0-8c1dfc234c07</t>
+  </si>
+  <si>
+    <t>0251dd88-0808-4850-af25-895508d530e9</t>
+  </si>
+  <si>
+    <t>4b8f1b76-555d-4721-bcf0-4948cd225462</t>
+  </si>
+  <si>
+    <t>07b3f568-7846-402d-a33e-45e13c010cad</t>
+  </si>
+  <si>
+    <t>96, LADERA EMERGENCY MA HELICOPTER MA KATHMANDU LAGEKO</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB206"/>
+  <dimension ref="A1:AB221"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -15916,6 +15961,1110 @@
         <v>15</v>
       </c>
     </row>
+    <row r="207" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>11299</v>
+      </c>
+      <c r="B207" t="s">
+        <v>246</v>
+      </c>
+      <c r="C207">
+        <v>3115</v>
+      </c>
+      <c r="D207">
+        <v>31304</v>
+      </c>
+      <c r="E207">
+        <v>4</v>
+      </c>
+      <c r="F207">
+        <v>2</v>
+      </c>
+      <c r="G207" t="s">
+        <v>169</v>
+      </c>
+      <c r="H207" t="s">
+        <v>30</v>
+      </c>
+      <c r="I207">
+        <v>25</v>
+      </c>
+      <c r="J207">
+        <v>54734</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="M207">
+        <v>6</v>
+      </c>
+      <c r="O207">
+        <v>0</v>
+      </c>
+      <c r="P207">
+        <v>0</v>
+      </c>
+      <c r="Q207">
+        <v>0</v>
+      </c>
+      <c r="R207">
+        <v>1000</v>
+      </c>
+      <c r="S207">
+        <v>2000</v>
+      </c>
+      <c r="T207">
+        <v>0</v>
+      </c>
+      <c r="U207">
+        <v>0</v>
+      </c>
+      <c r="V207">
+        <v>0</v>
+      </c>
+      <c r="W207">
+        <v>0</v>
+      </c>
+      <c r="X207">
+        <v>0</v>
+      </c>
+      <c r="Y207">
+        <v>3000</v>
+      </c>
+      <c r="Z207">
+        <v>4</v>
+      </c>
+      <c r="AA207">
+        <v>1</v>
+      </c>
+      <c r="AB207">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>11381</v>
+      </c>
+      <c r="B208" t="s">
+        <v>247</v>
+      </c>
+      <c r="C208">
+        <v>3454</v>
+      </c>
+      <c r="D208">
+        <v>30608</v>
+      </c>
+      <c r="E208">
+        <v>30</v>
+      </c>
+      <c r="F208">
+        <v>34</v>
+      </c>
+      <c r="G208" t="s">
+        <v>169</v>
+      </c>
+      <c r="H208" t="s">
+        <v>30</v>
+      </c>
+      <c r="I208">
+        <v>91</v>
+      </c>
+      <c r="J208">
+        <v>55077</v>
+      </c>
+      <c r="L208">
+        <v>2</v>
+      </c>
+      <c r="M208">
+        <v>13</v>
+      </c>
+      <c r="O208">
+        <v>11000</v>
+      </c>
+      <c r="P208">
+        <v>0</v>
+      </c>
+      <c r="Q208">
+        <v>0</v>
+      </c>
+      <c r="R208">
+        <v>0</v>
+      </c>
+      <c r="S208">
+        <v>0</v>
+      </c>
+      <c r="T208">
+        <v>0</v>
+      </c>
+      <c r="U208">
+        <v>0</v>
+      </c>
+      <c r="V208">
+        <v>5000</v>
+      </c>
+      <c r="W208">
+        <v>0</v>
+      </c>
+      <c r="X208">
+        <v>0</v>
+      </c>
+      <c r="Y208">
+        <v>16000</v>
+      </c>
+      <c r="Z208">
+        <v>4</v>
+      </c>
+      <c r="AA208">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>11499</v>
+      </c>
+      <c r="B209" t="s">
+        <v>248</v>
+      </c>
+      <c r="C209">
+        <v>3213</v>
+      </c>
+      <c r="D209">
+        <v>31301</v>
+      </c>
+      <c r="E209">
+        <v>7</v>
+      </c>
+      <c r="F209">
+        <v>16</v>
+      </c>
+      <c r="G209" t="s">
+        <v>169</v>
+      </c>
+      <c r="H209" t="s">
+        <v>30</v>
+      </c>
+      <c r="I209">
+        <v>26</v>
+      </c>
+      <c r="J209">
+        <v>55599</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209" t="s">
+        <v>249</v>
+      </c>
+      <c r="O209">
+        <v>100</v>
+      </c>
+      <c r="P209">
+        <v>1000</v>
+      </c>
+      <c r="Q209">
+        <v>15000</v>
+      </c>
+      <c r="R209">
+        <v>10000</v>
+      </c>
+      <c r="S209">
+        <v>50000</v>
+      </c>
+      <c r="T209">
+        <v>30000</v>
+      </c>
+      <c r="U209">
+        <v>5000</v>
+      </c>
+      <c r="V209">
+        <v>10000</v>
+      </c>
+      <c r="W209">
+        <v>10000</v>
+      </c>
+      <c r="X209">
+        <v>0</v>
+      </c>
+      <c r="Y209">
+        <v>131100</v>
+      </c>
+      <c r="Z209">
+        <v>3</v>
+      </c>
+      <c r="AA209">
+        <v>1</v>
+      </c>
+      <c r="AB209">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="210" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>11502</v>
+      </c>
+      <c r="B210" t="s">
+        <v>250</v>
+      </c>
+      <c r="C210">
+        <v>3213</v>
+      </c>
+      <c r="D210">
+        <v>31301</v>
+      </c>
+      <c r="E210">
+        <v>7</v>
+      </c>
+      <c r="F210">
+        <v>19</v>
+      </c>
+      <c r="G210" t="s">
+        <v>169</v>
+      </c>
+      <c r="H210" t="s">
+        <v>30</v>
+      </c>
+      <c r="I210">
+        <v>26</v>
+      </c>
+      <c r="J210">
+        <v>55612</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>2</v>
+      </c>
+      <c r="O210">
+        <v>0</v>
+      </c>
+      <c r="P210">
+        <v>500</v>
+      </c>
+      <c r="Q210">
+        <v>0</v>
+      </c>
+      <c r="R210">
+        <v>10000</v>
+      </c>
+      <c r="S210">
+        <v>15000</v>
+      </c>
+      <c r="T210">
+        <v>5000</v>
+      </c>
+      <c r="U210">
+        <v>5000</v>
+      </c>
+      <c r="V210">
+        <v>5000</v>
+      </c>
+      <c r="W210">
+        <v>0</v>
+      </c>
+      <c r="Y210">
+        <v>40500</v>
+      </c>
+      <c r="Z210">
+        <v>4</v>
+      </c>
+      <c r="AA210">
+        <v>1</v>
+      </c>
+      <c r="AB210">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>11566</v>
+      </c>
+      <c r="B211" t="s">
+        <v>251</v>
+      </c>
+      <c r="C211">
+        <v>5110</v>
+      </c>
+      <c r="D211">
+        <v>51106</v>
+      </c>
+      <c r="E211">
+        <v>20</v>
+      </c>
+      <c r="F211">
+        <v>35</v>
+      </c>
+      <c r="G211" t="s">
+        <v>169</v>
+      </c>
+      <c r="H211" t="s">
+        <v>30</v>
+      </c>
+      <c r="I211">
+        <v>44</v>
+      </c>
+      <c r="J211">
+        <v>55940</v>
+      </c>
+      <c r="L211">
+        <v>1</v>
+      </c>
+      <c r="M211">
+        <v>14</v>
+      </c>
+      <c r="Y211">
+        <v>50000</v>
+      </c>
+      <c r="Z211">
+        <v>4</v>
+      </c>
+      <c r="AA211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>11593</v>
+      </c>
+      <c r="B212" t="s">
+        <v>252</v>
+      </c>
+      <c r="C212">
+        <v>5110</v>
+      </c>
+      <c r="D212">
+        <v>51106</v>
+      </c>
+      <c r="E212">
+        <v>20</v>
+      </c>
+      <c r="F212">
+        <v>34</v>
+      </c>
+      <c r="G212" t="s">
+        <v>169</v>
+      </c>
+      <c r="H212" t="s">
+        <v>30</v>
+      </c>
+      <c r="I212">
+        <v>51</v>
+      </c>
+      <c r="J212">
+        <v>56076</v>
+      </c>
+      <c r="L212">
+        <v>1</v>
+      </c>
+      <c r="M212">
+        <v>4</v>
+      </c>
+      <c r="O212">
+        <v>0</v>
+      </c>
+      <c r="P212">
+        <v>5</v>
+      </c>
+      <c r="Q212">
+        <v>5000</v>
+      </c>
+      <c r="R212">
+        <v>5000</v>
+      </c>
+      <c r="S212">
+        <v>10000</v>
+      </c>
+      <c r="T212">
+        <v>0</v>
+      </c>
+      <c r="U212">
+        <v>1500</v>
+      </c>
+      <c r="V212">
+        <v>3000</v>
+      </c>
+      <c r="W212">
+        <v>0</v>
+      </c>
+      <c r="X212">
+        <v>0</v>
+      </c>
+      <c r="Y212">
+        <v>24505</v>
+      </c>
+      <c r="Z212">
+        <v>4</v>
+      </c>
+      <c r="AA212">
+        <v>1</v>
+      </c>
+      <c r="AB212">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>11684</v>
+      </c>
+      <c r="B213" t="s">
+        <v>253</v>
+      </c>
+      <c r="C213">
+        <v>5210</v>
+      </c>
+      <c r="D213">
+        <v>51106</v>
+      </c>
+      <c r="E213">
+        <v>20</v>
+      </c>
+      <c r="F213">
+        <v>39</v>
+      </c>
+      <c r="G213" t="s">
+        <v>169</v>
+      </c>
+      <c r="H213" t="s">
+        <v>30</v>
+      </c>
+      <c r="I213">
+        <v>51</v>
+      </c>
+      <c r="J213">
+        <v>56479</v>
+      </c>
+      <c r="L213">
+        <v>1</v>
+      </c>
+      <c r="M213">
+        <v>4</v>
+      </c>
+      <c r="O213">
+        <v>0</v>
+      </c>
+      <c r="P213">
+        <v>700</v>
+      </c>
+      <c r="Q213">
+        <v>2500</v>
+      </c>
+      <c r="R213">
+        <v>0</v>
+      </c>
+      <c r="S213">
+        <v>5000</v>
+      </c>
+      <c r="T213">
+        <v>0</v>
+      </c>
+      <c r="U213">
+        <v>800</v>
+      </c>
+      <c r="V213">
+        <v>1000</v>
+      </c>
+      <c r="W213">
+        <v>0</v>
+      </c>
+      <c r="X213">
+        <v>500</v>
+      </c>
+      <c r="Y213">
+        <v>10500</v>
+      </c>
+      <c r="Z213">
+        <v>4</v>
+      </c>
+      <c r="AA213">
+        <v>1</v>
+      </c>
+      <c r="AB213">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>11748</v>
+      </c>
+      <c r="B214" t="s">
+        <v>254</v>
+      </c>
+      <c r="C214">
+        <v>1107</v>
+      </c>
+      <c r="D214">
+        <v>11102</v>
+      </c>
+      <c r="E214">
+        <v>3</v>
+      </c>
+      <c r="F214">
+        <v>47</v>
+      </c>
+      <c r="G214" t="s">
+        <v>169</v>
+      </c>
+      <c r="H214" t="s">
+        <v>30</v>
+      </c>
+      <c r="I214">
+        <v>11</v>
+      </c>
+      <c r="J214">
+        <v>56783</v>
+      </c>
+      <c r="L214">
+        <v>2</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
+      </c>
+      <c r="Q214">
+        <v>11000</v>
+      </c>
+      <c r="S214">
+        <v>72000</v>
+      </c>
+      <c r="X214">
+        <v>25000</v>
+      </c>
+      <c r="Y214">
+        <v>108000</v>
+      </c>
+      <c r="Z214">
+        <v>1</v>
+      </c>
+      <c r="AA214">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>11834</v>
+      </c>
+      <c r="B215" t="s">
+        <v>255</v>
+      </c>
+      <c r="C215">
+        <v>1102</v>
+      </c>
+      <c r="D215">
+        <v>10304</v>
+      </c>
+      <c r="E215">
+        <v>4</v>
+      </c>
+      <c r="F215">
+        <v>42</v>
+      </c>
+      <c r="G215" t="s">
+        <v>169</v>
+      </c>
+      <c r="H215" t="s">
+        <v>30</v>
+      </c>
+      <c r="I215">
+        <v>13</v>
+      </c>
+      <c r="J215">
+        <v>57265</v>
+      </c>
+      <c r="L215">
+        <v>1</v>
+      </c>
+      <c r="M215">
+        <v>2</v>
+      </c>
+      <c r="O215">
+        <v>550</v>
+      </c>
+      <c r="P215">
+        <v>0</v>
+      </c>
+      <c r="Q215">
+        <v>3000</v>
+      </c>
+      <c r="R215">
+        <v>22000</v>
+      </c>
+      <c r="S215">
+        <v>8000</v>
+      </c>
+      <c r="T215">
+        <v>0</v>
+      </c>
+      <c r="U215">
+        <v>150000</v>
+      </c>
+      <c r="V215">
+        <v>0</v>
+      </c>
+      <c r="W215">
+        <v>32000</v>
+      </c>
+      <c r="X215">
+        <v>50000</v>
+      </c>
+      <c r="Y215">
+        <v>265550</v>
+      </c>
+      <c r="Z215">
+        <v>4</v>
+      </c>
+      <c r="AA215">
+        <v>1</v>
+      </c>
+      <c r="AB215">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>11900</v>
+      </c>
+      <c r="B216" t="s">
+        <v>256</v>
+      </c>
+      <c r="C216">
+        <v>4207</v>
+      </c>
+      <c r="D216">
+        <v>40806</v>
+      </c>
+      <c r="E216">
+        <v>14</v>
+      </c>
+      <c r="F216">
+        <v>33</v>
+      </c>
+      <c r="G216" t="s">
+        <v>169</v>
+      </c>
+      <c r="H216" t="s">
+        <v>30</v>
+      </c>
+      <c r="I216">
+        <v>26</v>
+      </c>
+      <c r="J216">
+        <v>57675</v>
+      </c>
+      <c r="L216">
+        <v>2</v>
+      </c>
+      <c r="M216">
+        <v>8</v>
+      </c>
+      <c r="Q216">
+        <v>25000</v>
+      </c>
+      <c r="R216">
+        <v>40000</v>
+      </c>
+      <c r="S216">
+        <v>25000</v>
+      </c>
+      <c r="T216">
+        <v>10000</v>
+      </c>
+      <c r="U216">
+        <v>15000</v>
+      </c>
+      <c r="V216">
+        <v>15000</v>
+      </c>
+      <c r="W216">
+        <v>0</v>
+      </c>
+      <c r="Y216">
+        <v>130000</v>
+      </c>
+      <c r="Z216">
+        <v>4</v>
+      </c>
+      <c r="AA216">
+        <v>1</v>
+      </c>
+      <c r="AB216">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>11917</v>
+      </c>
+      <c r="B217" t="s">
+        <v>257</v>
+      </c>
+      <c r="C217">
+        <v>7103</v>
+      </c>
+      <c r="D217">
+        <v>70403</v>
+      </c>
+      <c r="E217">
+        <v>7</v>
+      </c>
+      <c r="F217">
+        <v>21</v>
+      </c>
+      <c r="G217" t="s">
+        <v>169</v>
+      </c>
+      <c r="H217" t="s">
+        <v>30</v>
+      </c>
+      <c r="I217">
+        <v>71</v>
+      </c>
+      <c r="J217">
+        <v>57749</v>
+      </c>
+      <c r="L217">
+        <v>2</v>
+      </c>
+      <c r="M217">
+        <v>1</v>
+      </c>
+      <c r="O217">
+        <v>0</v>
+      </c>
+      <c r="P217">
+        <v>1500</v>
+      </c>
+      <c r="Q217">
+        <v>5800</v>
+      </c>
+      <c r="R217">
+        <v>12000</v>
+      </c>
+      <c r="S217">
+        <v>35000</v>
+      </c>
+      <c r="T217">
+        <v>0</v>
+      </c>
+      <c r="U217">
+        <v>30000</v>
+      </c>
+      <c r="V217">
+        <v>18000</v>
+      </c>
+      <c r="W217">
+        <v>0</v>
+      </c>
+      <c r="X217">
+        <v>15000</v>
+      </c>
+      <c r="Y217">
+        <v>117300</v>
+      </c>
+      <c r="Z217">
+        <v>1</v>
+      </c>
+      <c r="AA217">
+        <v>1</v>
+      </c>
+      <c r="AB217">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="218" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>11917</v>
+      </c>
+      <c r="B218" t="s">
+        <v>257</v>
+      </c>
+      <c r="C218">
+        <v>7103</v>
+      </c>
+      <c r="D218">
+        <v>70403</v>
+      </c>
+      <c r="E218">
+        <v>7</v>
+      </c>
+      <c r="F218">
+        <v>21</v>
+      </c>
+      <c r="G218" t="s">
+        <v>169</v>
+      </c>
+      <c r="H218" t="s">
+        <v>30</v>
+      </c>
+      <c r="I218">
+        <v>71</v>
+      </c>
+      <c r="J218">
+        <v>57749</v>
+      </c>
+      <c r="L218">
+        <v>2</v>
+      </c>
+      <c r="M218">
+        <v>2</v>
+      </c>
+      <c r="O218">
+        <v>0</v>
+      </c>
+      <c r="P218">
+        <v>500</v>
+      </c>
+      <c r="Q218">
+        <v>0</v>
+      </c>
+      <c r="R218">
+        <v>1400</v>
+      </c>
+      <c r="S218">
+        <v>13000</v>
+      </c>
+      <c r="T218">
+        <v>0</v>
+      </c>
+      <c r="U218">
+        <v>8000</v>
+      </c>
+      <c r="V218">
+        <v>1200</v>
+      </c>
+      <c r="W218">
+        <v>0</v>
+      </c>
+      <c r="X218">
+        <v>1000</v>
+      </c>
+      <c r="Y218">
+        <v>25100</v>
+      </c>
+      <c r="Z218">
+        <v>1</v>
+      </c>
+      <c r="AA218">
+        <v>1</v>
+      </c>
+      <c r="AB218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>11917</v>
+      </c>
+      <c r="B219" t="s">
+        <v>257</v>
+      </c>
+      <c r="C219">
+        <v>7103</v>
+      </c>
+      <c r="D219">
+        <v>70403</v>
+      </c>
+      <c r="E219">
+        <v>7</v>
+      </c>
+      <c r="F219">
+        <v>21</v>
+      </c>
+      <c r="G219" t="s">
+        <v>169</v>
+      </c>
+      <c r="H219" t="s">
+        <v>30</v>
+      </c>
+      <c r="I219">
+        <v>71</v>
+      </c>
+      <c r="J219">
+        <v>57749</v>
+      </c>
+      <c r="L219">
+        <v>2</v>
+      </c>
+      <c r="M219">
+        <v>12</v>
+      </c>
+      <c r="O219">
+        <v>0</v>
+      </c>
+      <c r="P219">
+        <v>500</v>
+      </c>
+      <c r="Q219">
+        <v>0</v>
+      </c>
+      <c r="R219">
+        <v>3500</v>
+      </c>
+      <c r="S219">
+        <v>13500</v>
+      </c>
+      <c r="T219">
+        <v>0</v>
+      </c>
+      <c r="U219">
+        <v>8000</v>
+      </c>
+      <c r="V219">
+        <v>2500</v>
+      </c>
+      <c r="W219">
+        <v>0</v>
+      </c>
+      <c r="X219">
+        <v>1200</v>
+      </c>
+      <c r="Y219">
+        <v>29200</v>
+      </c>
+      <c r="Z219">
+        <v>1</v>
+      </c>
+      <c r="AA219">
+        <v>1</v>
+      </c>
+      <c r="AB219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>11966</v>
+      </c>
+      <c r="B220" t="s">
+        <v>258</v>
+      </c>
+      <c r="C220">
+        <v>4107</v>
+      </c>
+      <c r="D220">
+        <v>40806</v>
+      </c>
+      <c r="E220">
+        <v>14</v>
+      </c>
+      <c r="F220">
+        <v>4</v>
+      </c>
+      <c r="G220" t="s">
+        <v>169</v>
+      </c>
+      <c r="H220" t="s">
+        <v>30</v>
+      </c>
+      <c r="I220">
+        <v>53</v>
+      </c>
+      <c r="J220">
+        <v>58008</v>
+      </c>
+      <c r="L220">
+        <v>1</v>
+      </c>
+      <c r="M220">
+        <v>2</v>
+      </c>
+      <c r="O220">
+        <v>150000</v>
+      </c>
+      <c r="P220">
+        <v>0</v>
+      </c>
+      <c r="Q220">
+        <v>0</v>
+      </c>
+      <c r="R220">
+        <v>0</v>
+      </c>
+      <c r="S220">
+        <v>0</v>
+      </c>
+      <c r="T220">
+        <v>0</v>
+      </c>
+      <c r="U220">
+        <v>0</v>
+      </c>
+      <c r="V220">
+        <v>0</v>
+      </c>
+      <c r="W220">
+        <v>0</v>
+      </c>
+      <c r="X220">
+        <v>0</v>
+      </c>
+      <c r="Y220">
+        <v>150000</v>
+      </c>
+      <c r="Z220">
+        <v>4</v>
+      </c>
+      <c r="AA220">
+        <v>1</v>
+      </c>
+      <c r="AB220">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="221" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>12012</v>
+      </c>
+      <c r="B221" t="s">
+        <v>259</v>
+      </c>
+      <c r="C221">
+        <v>1102</v>
+      </c>
+      <c r="D221">
+        <v>10304</v>
+      </c>
+      <c r="E221">
+        <v>4</v>
+      </c>
+      <c r="F221">
+        <v>45</v>
+      </c>
+      <c r="G221" t="s">
+        <v>169</v>
+      </c>
+      <c r="H221" t="s">
+        <v>30</v>
+      </c>
+      <c r="I221">
+        <v>14</v>
+      </c>
+      <c r="J221">
+        <v>58236</v>
+      </c>
+      <c r="L221">
+        <v>4</v>
+      </c>
+      <c r="M221" t="s">
+        <v>260</v>
+      </c>
+      <c r="U221">
+        <v>280000</v>
+      </c>
+      <c r="X221">
+        <v>700000</v>
+      </c>
+      <c r="Y221">
+        <v>980000</v>
+      </c>
+      <c r="Z221">
+        <v>4</v>
+      </c>
+      <c r="AA221">
+        <v>1</v>
+      </c>
+      <c r="AB221">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB206">

--- a/dataset/Part 6_2_4_ Chronic Illness and Expenditure Tracking – Inpatient.xlsx
+++ b/dataset/Part 6_2_4_ Chronic Illness and Expenditure Tracking – Inpatient.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-18-today\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-28-today (1)\2025-11-28-today\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D8B644-8ACD-4C20-9372-41A73130A95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5EB944-D234-4611-A4FC-382E12820AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="277">
   <si>
     <t>ID</t>
   </si>
@@ -814,6 +814,54 @@
   </si>
   <si>
     <t>96, LADERA EMERGENCY MA HELICOPTER MA KATHMANDU LAGEKO</t>
+  </si>
+  <si>
+    <t>f2558f0e-498c-47ce-bc80-333300a05b55</t>
+  </si>
+  <si>
+    <t>46312954-42c9-44eb-a0ee-f0ba9f412962</t>
+  </si>
+  <si>
+    <t>1eb40a8e-d33b-498c-b385-df3b1673a31a</t>
+  </si>
+  <si>
+    <t>ec242103-325c-4314-a982-dc8c419821a8</t>
+  </si>
+  <si>
+    <t>d207c664-e237-44fd-a07f-2c8ac4e80020</t>
+  </si>
+  <si>
+    <t>9b4213f6-17b1-471f-ab72-6fb284f672ca</t>
+  </si>
+  <si>
+    <t>b911d2c5-ffb0-4405-87e1-ae6df30b2707</t>
+  </si>
+  <si>
+    <t>58499b69-d22b-4d9e-8246-5a42ac197e8b</t>
+  </si>
+  <si>
+    <t>ec77fb99-1db9-4fec-974b-a78848504df5</t>
+  </si>
+  <si>
+    <t>e2103c32-9b07-490f-8111-045881bf3858</t>
+  </si>
+  <si>
+    <t>2362fdff-e736-4feb-89da-04c48b9f8e40</t>
+  </si>
+  <si>
+    <t>793fddc2-4e4b-4246-b3bc-28bad835d027</t>
+  </si>
+  <si>
+    <t>6a349f4b-c486-470e-97d6-4f1e1383318b</t>
+  </si>
+  <si>
+    <t>96, LIBAR KO SAMSYA</t>
+  </si>
+  <si>
+    <t>7cc133c6-a985-40bf-a8ef-94d7d505e1b2</t>
+  </si>
+  <si>
+    <t>72cc6d5e-78c4-4e56-92c0-5b14caef9344</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB221"/>
+  <dimension ref="A1:AB236"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -17065,6 +17113,1086 @@
         <v>60</v>
       </c>
     </row>
+    <row r="222" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>12142</v>
+      </c>
+      <c r="B222" t="s">
+        <v>261</v>
+      </c>
+      <c r="C222">
+        <v>2501</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>35</v>
+      </c>
+      <c r="G222" t="s">
+        <v>169</v>
+      </c>
+      <c r="H222" t="s">
+        <v>30</v>
+      </c>
+      <c r="I222">
+        <v>21</v>
+      </c>
+      <c r="J222">
+        <v>58922</v>
+      </c>
+      <c r="L222">
+        <v>2</v>
+      </c>
+      <c r="M222">
+        <v>2</v>
+      </c>
+      <c r="O222">
+        <v>0</v>
+      </c>
+      <c r="P222">
+        <v>0</v>
+      </c>
+      <c r="Q222">
+        <v>7000</v>
+      </c>
+      <c r="R222">
+        <v>0</v>
+      </c>
+      <c r="S222">
+        <v>3000</v>
+      </c>
+      <c r="T222">
+        <v>0</v>
+      </c>
+      <c r="U222">
+        <v>0</v>
+      </c>
+      <c r="V222">
+        <v>0</v>
+      </c>
+      <c r="W222">
+        <v>0</v>
+      </c>
+      <c r="X222">
+        <v>0</v>
+      </c>
+      <c r="Y222">
+        <v>10000</v>
+      </c>
+      <c r="Z222">
+        <v>1</v>
+      </c>
+      <c r="AA222">
+        <v>1</v>
+      </c>
+      <c r="AB222">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>12187</v>
+      </c>
+      <c r="B223" t="s">
+        <v>262</v>
+      </c>
+      <c r="C223">
+        <v>3604</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+      <c r="F223">
+        <v>71</v>
+      </c>
+      <c r="G223" t="s">
+        <v>169</v>
+      </c>
+      <c r="H223" t="s">
+        <v>30</v>
+      </c>
+      <c r="I223">
+        <v>91</v>
+      </c>
+      <c r="J223">
+        <v>59143</v>
+      </c>
+      <c r="L223">
+        <v>5</v>
+      </c>
+      <c r="M223">
+        <v>4</v>
+      </c>
+      <c r="O223">
+        <v>80000</v>
+      </c>
+      <c r="P223">
+        <v>0</v>
+      </c>
+      <c r="Q223">
+        <v>0</v>
+      </c>
+      <c r="R223">
+        <v>0</v>
+      </c>
+      <c r="S223">
+        <v>0</v>
+      </c>
+      <c r="T223">
+        <v>0</v>
+      </c>
+      <c r="U223">
+        <v>1000</v>
+      </c>
+      <c r="V223">
+        <v>0</v>
+      </c>
+      <c r="W223">
+        <v>0</v>
+      </c>
+      <c r="X223">
+        <v>0</v>
+      </c>
+      <c r="Y223">
+        <v>81000</v>
+      </c>
+      <c r="Z223">
+        <v>3</v>
+      </c>
+      <c r="AA223">
+        <v>1</v>
+      </c>
+      <c r="AB223">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="224" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>12230</v>
+      </c>
+      <c r="B224" t="s">
+        <v>263</v>
+      </c>
+      <c r="C224">
+        <v>7103</v>
+      </c>
+      <c r="D224">
+        <v>70403</v>
+      </c>
+      <c r="E224">
+        <v>7</v>
+      </c>
+      <c r="F224">
+        <v>28</v>
+      </c>
+      <c r="G224" t="s">
+        <v>169</v>
+      </c>
+      <c r="H224" t="s">
+        <v>30</v>
+      </c>
+      <c r="I224">
+        <v>71</v>
+      </c>
+      <c r="J224">
+        <v>59317</v>
+      </c>
+      <c r="L224">
+        <v>1</v>
+      </c>
+      <c r="M224">
+        <v>4</v>
+      </c>
+      <c r="O224">
+        <v>0</v>
+      </c>
+      <c r="P224">
+        <v>1400</v>
+      </c>
+      <c r="Q224">
+        <v>3400</v>
+      </c>
+      <c r="R224">
+        <v>1550</v>
+      </c>
+      <c r="S224">
+        <v>8000</v>
+      </c>
+      <c r="T224">
+        <v>2500</v>
+      </c>
+      <c r="U224">
+        <v>8000</v>
+      </c>
+      <c r="V224">
+        <v>2200</v>
+      </c>
+      <c r="W224">
+        <v>0</v>
+      </c>
+      <c r="X224">
+        <v>1500</v>
+      </c>
+      <c r="Y224">
+        <v>28550</v>
+      </c>
+      <c r="Z224">
+        <v>1</v>
+      </c>
+      <c r="AA224">
+        <v>1</v>
+      </c>
+      <c r="AB224">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="225" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>13502</v>
+      </c>
+      <c r="B225" t="s">
+        <v>264</v>
+      </c>
+      <c r="C225">
+        <v>2106</v>
+      </c>
+      <c r="D225">
+        <v>20514</v>
+      </c>
+      <c r="E225">
+        <v>2</v>
+      </c>
+      <c r="F225">
+        <v>43</v>
+      </c>
+      <c r="G225" t="s">
+        <v>169</v>
+      </c>
+      <c r="H225" t="s">
+        <v>30</v>
+      </c>
+      <c r="I225">
+        <v>28</v>
+      </c>
+      <c r="J225">
+        <v>5948329</v>
+      </c>
+      <c r="L225">
+        <v>6</v>
+      </c>
+      <c r="M225">
+        <v>2</v>
+      </c>
+      <c r="O225">
+        <v>13000</v>
+      </c>
+      <c r="S225">
+        <v>12000</v>
+      </c>
+      <c r="X225">
+        <v>12000</v>
+      </c>
+      <c r="Y225">
+        <v>37000</v>
+      </c>
+      <c r="Z225">
+        <v>1</v>
+      </c>
+      <c r="AA225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>13513</v>
+      </c>
+      <c r="B226" t="s">
+        <v>265</v>
+      </c>
+      <c r="C226">
+        <v>3470</v>
+      </c>
+      <c r="D226">
+        <v>30605</v>
+      </c>
+      <c r="E226">
+        <v>8</v>
+      </c>
+      <c r="F226">
+        <v>48</v>
+      </c>
+      <c r="G226" t="s">
+        <v>169</v>
+      </c>
+      <c r="H226" t="s">
+        <v>30</v>
+      </c>
+      <c r="I226">
+        <v>51</v>
+      </c>
+      <c r="J226">
+        <v>5948392</v>
+      </c>
+      <c r="L226">
+        <v>4</v>
+      </c>
+      <c r="M226">
+        <v>4</v>
+      </c>
+      <c r="O226">
+        <v>15000</v>
+      </c>
+      <c r="P226">
+        <v>20</v>
+      </c>
+      <c r="Q226">
+        <v>0</v>
+      </c>
+      <c r="R226">
+        <v>0</v>
+      </c>
+      <c r="S226">
+        <v>0</v>
+      </c>
+      <c r="T226">
+        <v>0</v>
+      </c>
+      <c r="U226">
+        <v>0</v>
+      </c>
+      <c r="V226">
+        <v>0</v>
+      </c>
+      <c r="W226">
+        <v>0</v>
+      </c>
+      <c r="X226">
+        <v>0</v>
+      </c>
+      <c r="Y226">
+        <v>15020</v>
+      </c>
+      <c r="Z226">
+        <v>1</v>
+      </c>
+      <c r="AA226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>13560</v>
+      </c>
+      <c r="B227" t="s">
+        <v>266</v>
+      </c>
+      <c r="C227">
+        <v>3470</v>
+      </c>
+      <c r="D227">
+        <v>30604</v>
+      </c>
+      <c r="E227">
+        <v>8</v>
+      </c>
+      <c r="F227">
+        <v>7</v>
+      </c>
+      <c r="G227" t="s">
+        <v>169</v>
+      </c>
+      <c r="H227" t="s">
+        <v>30</v>
+      </c>
+      <c r="I227">
+        <v>53</v>
+      </c>
+      <c r="J227">
+        <v>5948626</v>
+      </c>
+      <c r="L227">
+        <v>5</v>
+      </c>
+      <c r="M227">
+        <v>4</v>
+      </c>
+      <c r="O227">
+        <v>70000</v>
+      </c>
+      <c r="P227">
+        <v>0</v>
+      </c>
+      <c r="Q227">
+        <v>0</v>
+      </c>
+      <c r="R227">
+        <v>0</v>
+      </c>
+      <c r="S227">
+        <v>0</v>
+      </c>
+      <c r="T227">
+        <v>0</v>
+      </c>
+      <c r="U227">
+        <v>0</v>
+      </c>
+      <c r="V227">
+        <v>0</v>
+      </c>
+      <c r="W227">
+        <v>0</v>
+      </c>
+      <c r="X227">
+        <v>0</v>
+      </c>
+      <c r="Y227">
+        <v>70000</v>
+      </c>
+      <c r="Z227">
+        <v>4</v>
+      </c>
+      <c r="AA227">
+        <v>1</v>
+      </c>
+      <c r="AB227">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>13564</v>
+      </c>
+      <c r="B228" t="s">
+        <v>267</v>
+      </c>
+      <c r="C228">
+        <v>3474</v>
+      </c>
+      <c r="E228">
+        <v>6</v>
+      </c>
+      <c r="F228">
+        <v>11</v>
+      </c>
+      <c r="G228" t="s">
+        <v>169</v>
+      </c>
+      <c r="H228" t="s">
+        <v>30</v>
+      </c>
+      <c r="I228">
+        <v>53</v>
+      </c>
+      <c r="J228">
+        <v>5948642</v>
+      </c>
+      <c r="L228">
+        <v>1</v>
+      </c>
+      <c r="M228">
+        <v>3</v>
+      </c>
+      <c r="O228">
+        <v>40000</v>
+      </c>
+      <c r="P228">
+        <v>0</v>
+      </c>
+      <c r="Q228">
+        <v>0</v>
+      </c>
+      <c r="R228">
+        <v>0</v>
+      </c>
+      <c r="S228">
+        <v>0</v>
+      </c>
+      <c r="T228">
+        <v>0</v>
+      </c>
+      <c r="U228">
+        <v>0</v>
+      </c>
+      <c r="V228">
+        <v>0</v>
+      </c>
+      <c r="W228">
+        <v>0</v>
+      </c>
+      <c r="X228">
+        <v>0</v>
+      </c>
+      <c r="Y228">
+        <v>40000</v>
+      </c>
+      <c r="Z228">
+        <v>1</v>
+      </c>
+      <c r="AA228">
+        <v>1</v>
+      </c>
+      <c r="AB228">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>13575</v>
+      </c>
+      <c r="B229" t="s">
+        <v>268</v>
+      </c>
+      <c r="C229">
+        <v>2106</v>
+      </c>
+      <c r="D229">
+        <v>20514</v>
+      </c>
+      <c r="E229">
+        <v>2</v>
+      </c>
+      <c r="F229">
+        <v>49</v>
+      </c>
+      <c r="G229" t="s">
+        <v>169</v>
+      </c>
+      <c r="H229" t="s">
+        <v>30</v>
+      </c>
+      <c r="I229">
+        <v>24</v>
+      </c>
+      <c r="J229">
+        <v>5948707</v>
+      </c>
+      <c r="L229">
+        <v>2</v>
+      </c>
+      <c r="M229">
+        <v>4</v>
+      </c>
+      <c r="O229">
+        <v>1</v>
+      </c>
+      <c r="P229">
+        <v>0</v>
+      </c>
+      <c r="Q229">
+        <v>0</v>
+      </c>
+      <c r="R229">
+        <v>0</v>
+      </c>
+      <c r="S229">
+        <v>0</v>
+      </c>
+      <c r="T229">
+        <v>0</v>
+      </c>
+      <c r="U229">
+        <v>0</v>
+      </c>
+      <c r="V229">
+        <v>0</v>
+      </c>
+      <c r="W229">
+        <v>0</v>
+      </c>
+      <c r="X229">
+        <v>0</v>
+      </c>
+      <c r="Y229">
+        <v>1</v>
+      </c>
+      <c r="Z229">
+        <v>1</v>
+      </c>
+      <c r="AA229">
+        <v>1</v>
+      </c>
+      <c r="AB229">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>13612</v>
+      </c>
+      <c r="B230" t="s">
+        <v>269</v>
+      </c>
+      <c r="C230">
+        <v>3600</v>
+      </c>
+      <c r="D230">
+        <v>30605</v>
+      </c>
+      <c r="E230">
+        <v>17</v>
+      </c>
+      <c r="F230">
+        <v>83</v>
+      </c>
+      <c r="G230" t="s">
+        <v>169</v>
+      </c>
+      <c r="H230" t="s">
+        <v>30</v>
+      </c>
+      <c r="I230">
+        <v>13</v>
+      </c>
+      <c r="J230">
+        <v>5948874</v>
+      </c>
+      <c r="L230">
+        <v>2</v>
+      </c>
+      <c r="M230">
+        <v>16</v>
+      </c>
+      <c r="O230">
+        <v>0</v>
+      </c>
+      <c r="P230">
+        <v>0</v>
+      </c>
+      <c r="Q230">
+        <v>0</v>
+      </c>
+      <c r="R230">
+        <v>0</v>
+      </c>
+      <c r="S230">
+        <v>0</v>
+      </c>
+      <c r="T230">
+        <v>0</v>
+      </c>
+      <c r="U230">
+        <v>0</v>
+      </c>
+      <c r="V230">
+        <v>0</v>
+      </c>
+      <c r="W230">
+        <v>0</v>
+      </c>
+      <c r="X230">
+        <v>0</v>
+      </c>
+      <c r="Y230">
+        <v>0</v>
+      </c>
+      <c r="Z230">
+        <v>4</v>
+      </c>
+      <c r="AA230">
+        <v>1</v>
+      </c>
+      <c r="AB230">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="231" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>13634</v>
+      </c>
+      <c r="B231" t="s">
+        <v>270</v>
+      </c>
+      <c r="C231">
+        <v>7104</v>
+      </c>
+      <c r="D231">
+        <v>70410</v>
+      </c>
+      <c r="E231">
+        <v>1</v>
+      </c>
+      <c r="F231">
+        <v>39</v>
+      </c>
+      <c r="G231" t="s">
+        <v>169</v>
+      </c>
+      <c r="H231" t="s">
+        <v>30</v>
+      </c>
+      <c r="I231">
+        <v>73</v>
+      </c>
+      <c r="J231">
+        <v>5948965</v>
+      </c>
+      <c r="L231">
+        <v>7</v>
+      </c>
+      <c r="M231">
+        <v>4</v>
+      </c>
+      <c r="O231">
+        <v>0</v>
+      </c>
+      <c r="P231">
+        <v>0</v>
+      </c>
+      <c r="Q231">
+        <v>2000</v>
+      </c>
+      <c r="R231">
+        <v>0</v>
+      </c>
+      <c r="S231">
+        <v>6000</v>
+      </c>
+      <c r="T231">
+        <v>0</v>
+      </c>
+      <c r="U231">
+        <v>10000</v>
+      </c>
+      <c r="V231">
+        <v>6000</v>
+      </c>
+      <c r="W231">
+        <v>0</v>
+      </c>
+      <c r="X231">
+        <v>4500</v>
+      </c>
+      <c r="Y231">
+        <v>28500</v>
+      </c>
+      <c r="Z231">
+        <v>4</v>
+      </c>
+      <c r="AA231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>13688</v>
+      </c>
+      <c r="B232" t="s">
+        <v>271</v>
+      </c>
+      <c r="C232">
+        <v>3310</v>
+      </c>
+      <c r="D232">
+        <v>31206</v>
+      </c>
+      <c r="E232">
+        <v>8</v>
+      </c>
+      <c r="F232">
+        <v>56</v>
+      </c>
+      <c r="G232" t="s">
+        <v>169</v>
+      </c>
+      <c r="H232" t="s">
+        <v>30</v>
+      </c>
+      <c r="I232">
+        <v>28</v>
+      </c>
+      <c r="J232">
+        <v>5949191</v>
+      </c>
+      <c r="L232">
+        <v>3</v>
+      </c>
+      <c r="M232">
+        <v>2</v>
+      </c>
+      <c r="O232">
+        <v>140000</v>
+      </c>
+      <c r="Y232">
+        <v>140000</v>
+      </c>
+      <c r="Z232">
+        <v>1</v>
+      </c>
+      <c r="AA232">
+        <v>1</v>
+      </c>
+      <c r="AB232">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="233" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>13689</v>
+      </c>
+      <c r="B233" t="s">
+        <v>272</v>
+      </c>
+      <c r="C233">
+        <v>3310</v>
+      </c>
+      <c r="D233">
+        <v>31206</v>
+      </c>
+      <c r="E233">
+        <v>8</v>
+      </c>
+      <c r="F233">
+        <v>57</v>
+      </c>
+      <c r="G233" t="s">
+        <v>169</v>
+      </c>
+      <c r="H233" t="s">
+        <v>30</v>
+      </c>
+      <c r="I233">
+        <v>28</v>
+      </c>
+      <c r="J233">
+        <v>5949198</v>
+      </c>
+      <c r="L233">
+        <v>5</v>
+      </c>
+      <c r="M233">
+        <v>96</v>
+      </c>
+      <c r="O233">
+        <v>200000</v>
+      </c>
+      <c r="Y233">
+        <v>200000</v>
+      </c>
+      <c r="Z233">
+        <v>96</v>
+      </c>
+      <c r="AA233">
+        <v>1</v>
+      </c>
+      <c r="AB233">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="234" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>13692</v>
+      </c>
+      <c r="B234" t="s">
+        <v>273</v>
+      </c>
+      <c r="C234">
+        <v>3410</v>
+      </c>
+      <c r="D234">
+        <v>31206</v>
+      </c>
+      <c r="E234">
+        <v>8</v>
+      </c>
+      <c r="F234">
+        <v>60</v>
+      </c>
+      <c r="G234" t="s">
+        <v>169</v>
+      </c>
+      <c r="H234" t="s">
+        <v>30</v>
+      </c>
+      <c r="I234">
+        <v>28</v>
+      </c>
+      <c r="J234">
+        <v>5949212</v>
+      </c>
+      <c r="L234">
+        <v>5</v>
+      </c>
+      <c r="M234" t="s">
+        <v>274</v>
+      </c>
+      <c r="O234">
+        <v>150000</v>
+      </c>
+      <c r="Y234">
+        <v>150000</v>
+      </c>
+      <c r="Z234">
+        <v>1</v>
+      </c>
+      <c r="AA234">
+        <v>1</v>
+      </c>
+      <c r="AB234">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="235" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>13731</v>
+      </c>
+      <c r="B235" t="s">
+        <v>275</v>
+      </c>
+      <c r="C235">
+        <v>3534</v>
+      </c>
+      <c r="D235">
+        <v>30802</v>
+      </c>
+      <c r="E235">
+        <v>18</v>
+      </c>
+      <c r="F235">
+        <v>29</v>
+      </c>
+      <c r="G235" t="s">
+        <v>169</v>
+      </c>
+      <c r="H235" t="s">
+        <v>30</v>
+      </c>
+      <c r="I235">
+        <v>55</v>
+      </c>
+      <c r="J235">
+        <v>5949372</v>
+      </c>
+      <c r="L235">
+        <v>1</v>
+      </c>
+      <c r="M235">
+        <v>2</v>
+      </c>
+      <c r="O235">
+        <v>0</v>
+      </c>
+      <c r="P235">
+        <v>0</v>
+      </c>
+      <c r="Q235">
+        <v>0</v>
+      </c>
+      <c r="R235">
+        <v>0</v>
+      </c>
+      <c r="S235">
+        <v>0</v>
+      </c>
+      <c r="T235">
+        <v>0</v>
+      </c>
+      <c r="U235">
+        <v>0</v>
+      </c>
+      <c r="V235">
+        <v>0</v>
+      </c>
+      <c r="W235">
+        <v>0</v>
+      </c>
+      <c r="X235">
+        <v>150000</v>
+      </c>
+      <c r="Y235">
+        <v>150000</v>
+      </c>
+      <c r="Z235">
+        <v>3</v>
+      </c>
+      <c r="AA235">
+        <v>1</v>
+      </c>
+      <c r="AB235">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="236" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>14008</v>
+      </c>
+      <c r="B236" t="s">
+        <v>276</v>
+      </c>
+      <c r="C236">
+        <v>3546</v>
+      </c>
+      <c r="D236">
+        <v>30803</v>
+      </c>
+      <c r="E236">
+        <v>14</v>
+      </c>
+      <c r="F236">
+        <v>37</v>
+      </c>
+      <c r="G236" t="s">
+        <v>169</v>
+      </c>
+      <c r="H236" t="s">
+        <v>30</v>
+      </c>
+      <c r="I236">
+        <v>55</v>
+      </c>
+      <c r="J236">
+        <v>5950536</v>
+      </c>
+      <c r="L236">
+        <v>1</v>
+      </c>
+      <c r="M236">
+        <v>1</v>
+      </c>
+      <c r="O236">
+        <v>0</v>
+      </c>
+      <c r="P236">
+        <v>0</v>
+      </c>
+      <c r="Q236">
+        <v>0</v>
+      </c>
+      <c r="R236">
+        <v>0</v>
+      </c>
+      <c r="S236">
+        <v>0</v>
+      </c>
+      <c r="T236">
+        <v>0</v>
+      </c>
+      <c r="U236">
+        <v>0</v>
+      </c>
+      <c r="V236">
+        <v>0</v>
+      </c>
+      <c r="W236">
+        <v>0</v>
+      </c>
+      <c r="X236">
+        <v>400000</v>
+      </c>
+      <c r="Y236">
+        <v>400000</v>
+      </c>
+      <c r="Z236">
+        <v>1</v>
+      </c>
+      <c r="AA236">
+        <v>1</v>
+      </c>
+      <c r="AB236">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB206">

--- a/dataset/Part 6_2_4_ Chronic Illness and Expenditure Tracking – Inpatient.xlsx
+++ b/dataset/Part 6_2_4_ Chronic Illness and Expenditure Tracking – Inpatient.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-12-10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CD243D-6EFA-4653-81E3-C459EF94A4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55825DD3-F1E4-4EDF-A224-B95DAD84E46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="307">
   <si>
     <t>ID</t>
   </si>
@@ -933,9 +933,6 @@
     <t>ce9cfc67-9cb1-4497-a1cc-1da50f5aa381</t>
   </si>
   <si>
-    <t>72cc6d5e-78c4-4e56-92c0-5b14caef9344</t>
-  </si>
-  <si>
     <t>233da1d5-5361-465a-981d-0ba8392a4066</t>
   </si>
   <si>
@@ -943,6 +940,18 @@
   </si>
   <si>
     <t>15a489ef-e286-45a9-be49-c1c5256ae412</t>
+  </si>
+  <si>
+    <t>a2ada03d-e25b-4809-9e4b-63f58380766f</t>
+  </si>
+  <si>
+    <t>a7c4859e-f91e-4cc6-83f0-f1c7a8a51382</t>
+  </si>
+  <si>
+    <t>0cb50145-2d2a-4aa6-b149-ae9d65fbf814</t>
+  </si>
+  <si>
+    <t>ALLERGY, 96</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB260"/>
+  <dimension ref="A1:AB262"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -11579,7 +11588,7 @@
         <v>184</v>
       </c>
       <c r="C144">
-        <v>4412</v>
+        <v>4404</v>
       </c>
       <c r="D144">
         <v>40504</v>
@@ -11656,7 +11665,7 @@
         <v>185</v>
       </c>
       <c r="C145">
-        <v>4402</v>
+        <v>4426</v>
       </c>
       <c r="D145">
         <v>40504</v>
@@ -17957,6 +17966,9 @@
       <c r="C233">
         <v>2501</v>
       </c>
+      <c r="D233">
+        <v>20302</v>
+      </c>
       <c r="E233">
         <v>0</v>
       </c>
@@ -18034,6 +18046,9 @@
       <c r="C234">
         <v>3604</v>
       </c>
+      <c r="D234">
+        <v>30608</v>
+      </c>
       <c r="E234">
         <v>0</v>
       </c>
@@ -18420,7 +18435,7 @@
         <v>5211</v>
       </c>
       <c r="D239">
-        <v>51108</v>
+        <v>51104</v>
       </c>
       <c r="E239">
         <v>3</v>
@@ -18896,10 +18911,13 @@
         <v>287</v>
       </c>
       <c r="C246">
-        <v>3474</v>
+        <v>3465</v>
+      </c>
+      <c r="D246">
+        <v>30703</v>
       </c>
       <c r="E246">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F246">
         <v>11</v>
@@ -19662,10 +19680,10 @@
         <v>5111</v>
       </c>
       <c r="D257">
-        <v>51108</v>
+        <v>51104</v>
       </c>
       <c r="E257">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F257">
         <v>34</v>
@@ -19706,22 +19724,22 @@
     </row>
     <row r="258" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>14185</v>
+        <v>14224</v>
       </c>
       <c r="B258" t="s">
         <v>300</v>
       </c>
       <c r="C258">
-        <v>3546</v>
+        <v>3310</v>
       </c>
       <c r="D258">
-        <v>30803</v>
+        <v>31206</v>
       </c>
       <c r="E258">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F258">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="G258" t="s">
         <v>169</v>
@@ -19730,26 +19748,23 @@
         <v>30</v>
       </c>
       <c r="I258">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="J258">
-        <v>5951398</v>
+        <v>5951539</v>
       </c>
       <c r="L258">
         <v>1</v>
       </c>
-      <c r="M258">
-        <v>1</v>
+      <c r="M258" t="s">
+        <v>301</v>
       </c>
       <c r="O258">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="P258">
         <v>0</v>
       </c>
-      <c r="Q258">
-        <v>0</v>
-      </c>
       <c r="R258">
         <v>0</v>
       </c>
@@ -19760,7 +19775,7 @@
         <v>0</v>
       </c>
       <c r="U258">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V258">
         <v>0</v>
@@ -19769,39 +19784,39 @@
         <v>0</v>
       </c>
       <c r="X258">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="Y258">
-        <v>400000</v>
+        <v>253000</v>
       </c>
       <c r="Z258">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA258">
         <v>1</v>
       </c>
       <c r="AB258">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="259" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>14224</v>
+        <v>14292</v>
       </c>
       <c r="B259" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C259">
-        <v>3310</v>
+        <v>6103</v>
       </c>
       <c r="D259">
-        <v>31206</v>
+        <v>60602</v>
       </c>
       <c r="E259">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F259">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="G259" t="s">
         <v>169</v>
@@ -19810,75 +19825,78 @@
         <v>30</v>
       </c>
       <c r="I259">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="J259">
-        <v>5951539</v>
+        <v>5951902</v>
       </c>
       <c r="L259">
-        <v>1</v>
-      </c>
-      <c r="M259" t="s">
-        <v>302</v>
+        <v>2</v>
+      </c>
+      <c r="M259">
+        <v>16</v>
       </c>
       <c r="O259">
-        <v>250000</v>
+        <v>200</v>
       </c>
       <c r="P259">
         <v>0</v>
       </c>
+      <c r="Q259">
+        <v>1000</v>
+      </c>
       <c r="R259">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="S259">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T259">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="U259">
-        <v>3000</v>
+        <v>32000</v>
       </c>
       <c r="V259">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="W259">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="X259">
         <v>0</v>
       </c>
       <c r="Y259">
-        <v>253000</v>
+        <v>91200</v>
       </c>
       <c r="Z259">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA259">
         <v>1</v>
       </c>
       <c r="AB259">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="260" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>14292</v>
+        <v>14366</v>
       </c>
       <c r="B260" t="s">
         <v>303</v>
       </c>
       <c r="C260">
-        <v>6103</v>
+        <v>6105</v>
       </c>
       <c r="D260">
-        <v>60602</v>
+        <v>60703</v>
       </c>
       <c r="E260">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F260">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G260" t="s">
         <v>169</v>
@@ -19887,57 +19905,217 @@
         <v>30</v>
       </c>
       <c r="I260">
+        <v>41</v>
+      </c>
+      <c r="J260">
+        <v>5952245</v>
+      </c>
+      <c r="L260">
+        <v>1</v>
+      </c>
+      <c r="M260" t="s">
+        <v>255</v>
+      </c>
+      <c r="O260">
+        <v>0</v>
+      </c>
+      <c r="P260">
+        <v>700</v>
+      </c>
+      <c r="Q260">
+        <v>8000</v>
+      </c>
+      <c r="R260">
+        <v>15000</v>
+      </c>
+      <c r="S260">
+        <v>12000</v>
+      </c>
+      <c r="T260">
+        <v>16000</v>
+      </c>
+      <c r="U260">
+        <v>15000</v>
+      </c>
+      <c r="V260">
+        <v>10000</v>
+      </c>
+      <c r="W260">
+        <v>0</v>
+      </c>
+      <c r="X260">
+        <v>5000</v>
+      </c>
+      <c r="Y260">
+        <v>81700</v>
+      </c>
+      <c r="Z260">
+        <v>1</v>
+      </c>
+      <c r="AA260">
+        <v>1</v>
+      </c>
+      <c r="AB260">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="261" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>14382</v>
+      </c>
+      <c r="B261" t="s">
+        <v>304</v>
+      </c>
+      <c r="C261">
+        <v>6105</v>
+      </c>
+      <c r="D261">
+        <v>60703</v>
+      </c>
+      <c r="E261">
+        <v>5</v>
+      </c>
+      <c r="F261">
+        <v>64</v>
+      </c>
+      <c r="G261" t="s">
+        <v>169</v>
+      </c>
+      <c r="H261" t="s">
+        <v>30</v>
+      </c>
+      <c r="I261">
         <v>61</v>
       </c>
-      <c r="J260">
-        <v>5951902</v>
-      </c>
-      <c r="L260">
-        <v>2</v>
-      </c>
-      <c r="M260">
-        <v>16</v>
-      </c>
-      <c r="O260">
-        <v>200</v>
-      </c>
-      <c r="P260">
-        <v>0</v>
-      </c>
-      <c r="Q260">
-        <v>1000</v>
-      </c>
-      <c r="R260">
+      <c r="J261">
+        <v>5952330</v>
+      </c>
+      <c r="L261">
+        <v>3</v>
+      </c>
+      <c r="M261">
+        <v>2</v>
+      </c>
+      <c r="O261">
+        <v>5000</v>
+      </c>
+      <c r="P261">
+        <v>0</v>
+      </c>
+      <c r="Q261">
+        <v>14500</v>
+      </c>
+      <c r="R261">
+        <v>14000</v>
+      </c>
+      <c r="S261">
+        <v>16000</v>
+      </c>
+      <c r="T261">
+        <v>0</v>
+      </c>
+      <c r="U261">
+        <v>30000</v>
+      </c>
+      <c r="V261">
+        <v>3000</v>
+      </c>
+      <c r="W261">
+        <v>0</v>
+      </c>
+      <c r="X261">
+        <v>0</v>
+      </c>
+      <c r="Y261">
+        <v>82500</v>
+      </c>
+      <c r="Z261">
+        <v>1</v>
+      </c>
+      <c r="AA261">
+        <v>1</v>
+      </c>
+      <c r="AB261">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>14512</v>
+      </c>
+      <c r="B262" t="s">
+        <v>305</v>
+      </c>
+      <c r="C262">
+        <v>6316</v>
+      </c>
+      <c r="D262">
+        <v>61006</v>
+      </c>
+      <c r="E262">
+        <v>4</v>
+      </c>
+      <c r="F262">
+        <v>51</v>
+      </c>
+      <c r="G262" t="s">
+        <v>169</v>
+      </c>
+      <c r="H262" t="s">
+        <v>30</v>
+      </c>
+      <c r="I262">
+        <v>73</v>
+      </c>
+      <c r="J262">
+        <v>5952839</v>
+      </c>
+      <c r="L262">
+        <v>2</v>
+      </c>
+      <c r="M262" t="s">
+        <v>306</v>
+      </c>
+      <c r="O262">
         <v>12000</v>
       </c>
-      <c r="S260">
-        <v>10000</v>
-      </c>
-      <c r="T260">
+      <c r="P262">
+        <v>1500</v>
+      </c>
+      <c r="Q262">
         <v>12000</v>
       </c>
-      <c r="U260">
-        <v>32000</v>
-      </c>
-      <c r="V260">
+      <c r="R262">
+        <v>4500</v>
+      </c>
+      <c r="S262">
+        <v>9000</v>
+      </c>
+      <c r="T262">
+        <v>0</v>
+      </c>
+      <c r="U262">
         <v>6000</v>
       </c>
-      <c r="W260">
-        <v>18000</v>
-      </c>
-      <c r="X260">
-        <v>0</v>
-      </c>
-      <c r="Y260">
-        <v>91200</v>
-      </c>
-      <c r="Z260">
-        <v>1</v>
-      </c>
-      <c r="AA260">
-        <v>1</v>
-      </c>
-      <c r="AB260">
+      <c r="V262">
+        <v>3000</v>
+      </c>
+      <c r="W262">
+        <v>0</v>
+      </c>
+      <c r="X262">
+        <v>0</v>
+      </c>
+      <c r="Y262">
+        <v>48000</v>
+      </c>
+      <c r="Z262">
+        <v>1</v>
+      </c>
+      <c r="AA262">
+        <v>1</v>
+      </c>
+      <c r="AB262">
         <v>15</v>
       </c>
     </row>
